--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
@@ -739,10 +739,10 @@
         <v>437.3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>31.2</v>
+        <v>21.2</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>17.2</v>
+        <v>1.3</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>24.2</v>
@@ -751,10 +751,10 @@
         <v>14</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>22.4</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>4.2</v>
@@ -766,32 +766,32 @@
       <c r="M4" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="N4" s="8" t="n">
+      <c r="N4" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>30</v>
+        <v>2.6</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>27</v>
+        <v>27.8</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>63.7</v>
       </c>
-      <c r="U4" s="8" t="n">
+      <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24</v>
@@ -800,7 +800,7 @@
         <v>27.5</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>9.699999999999999</v>
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>62.9</v>
+        <v>62.3</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>18.7</v>
+        <v>18.2</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>5.7</v>
+        <v>57.2</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>16.3</v>
@@ -849,19 +849,19 @@
         <v>19.1</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>18</v>
+        <v>0.6</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>90</v>
+        <v>96.2</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>2.3</v>
+        <v>24.3</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>20.5</v>
+        <v>22.5</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>19.1</v>
@@ -870,13 +870,13 @@
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>87.8</v>
+        <v>82.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>60.6</v>
+        <v>61.6</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>18.9</v>
@@ -885,7 +885,7 @@
         <v>20.7</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>3.6</v>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>438.6</v>
+        <v>431.6</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>31.4</v>
@@ -916,23 +916,25 @@
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>17.8</v>
+        <v>12.8</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J6" s="3" t="n"/>
+      <c r="J6" s="3" t="n">
+        <v>3.6</v>
+      </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>60.6</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <v>19</v>
+      <c r="M6" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>21.1</v>
@@ -941,7 +943,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>29.8</v>
@@ -955,7 +957,7 @@
       <c r="T6" s="3" t="n">
         <v>61.9</v>
       </c>
-      <c r="U6" s="8" t="n">
+      <c r="U6" s="3" t="n">
         <v>16</v>
       </c>
       <c r="V6" s="3" t="n">
@@ -968,10 +970,10 @@
         <v>26.5</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>11.9</v>
+        <v>11.1</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -993,16 +995,16 @@
         <v>33</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.1</v>
+        <v>8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>14.8</v>
+      <c r="H7" s="3" t="n">
+        <v>4.2</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>3.4</v>
@@ -1011,25 +1013,25 @@
         <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L7" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="N7" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>17.3</v>
-      </c>
       <c r="O7" s="3" t="n">
-        <v>872.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" s="3" t="n">
-        <v>31.9</v>
+      <c r="Q7" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>23.9</v>
@@ -1038,25 +1040,25 @@
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>52.1</v>
+        <v>5.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>27.6</v>
+        <v>6.6</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>4.1</v>
+        <v>24.1</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>27.8</v>
+        <v>2.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>75.2</v>
+        <v>5.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1072,46 +1074,46 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>297.2</v>
+        <v>0.4</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>32.6</v>
+        <v>52.6</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>19.8</v>
+        <v>0.4</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>26.2</v>
+        <v>86.2</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.1</v>
+        <v>4.4</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>18.5</v>
+        <v>24.5</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>18.6</v>
+      <c r="M8" s="8" t="n">
+        <v>865.6</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>87.2</v>
+        <v>82.7</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>21.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>26.6</v>
@@ -1126,22 +1128,22 @@
         <v>95.40000000000001</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>24</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>212.4</v>
+        <v>22.8</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>90.2</v>
+        <v>96.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>2.9</v>
+        <v>8.9</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1157,25 +1159,23 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>6663.1</v>
+        <v>6.6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>52.1</v>
+        <v>32.6</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>192.5</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>22.5</v>
-      </c>
+        <v>92.5</v>
+      </c>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n">
-        <v>60.1</v>
+        <v>611.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>80.5</v>
+        <v>86.5</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>11.2</v>
+        <v>4.4</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
@@ -1187,7 +1187,7 @@
         <v>94.3</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>87.8</v>
+        <v>82.8</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>96.3</v>
@@ -1196,7 +1196,7 @@
         <v>440.9</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>4.4</v>
+        <v>12.9</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>138.8</v>
@@ -1205,7 +1205,7 @@
         <v>11.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>344.1</v>
+        <v>31.9</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>360.9</v>
@@ -1217,13 +1217,13 @@
         <v>126.1</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>29.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>2.8</v>
@@ -1242,38 +1242,40 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>333.3</v>
+        <v>333.2</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>30.5</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>16.1</v>
+        <v>1.6</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
+        <v>3.4</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>44.7</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="8" t="n">
-        <v>17.6</v>
+      <c r="M10" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>19.3</v>
+        <v>1.3</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>88.2</v>
@@ -1282,31 +1284,31 @@
         <v>2.6</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>27.8</v>
+        <v>82.2</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>26.4</v>
+        <v>2.6</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>11.7</v>
+        <v>2.2</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>25.2</v>
+        <v>25.8</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>22.6</v>
+        <v>2.6</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>80.5</v>
+        <v>806.5</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>6.6</v>
@@ -1325,19 +1327,19 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>445</v>
+        <v>445.6</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>19.9</v>
+        <v>4.2</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>92.90000000000001</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>18.2</v>
@@ -1346,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>31.3</v>
+        <v>3.3</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1357,7 +1359,9 @@
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="N11" s="3" t="n"/>
+      <c r="N11" s="3" t="n">
+        <v>10.7</v>
+      </c>
       <c r="O11" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
@@ -1367,14 +1371,14 @@
       <c r="Q11" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="R11" s="8" t="n">
+      <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>5.7</v>
@@ -1385,11 +1389,11 @@
       <c r="W11" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="X11" s="8" t="n">
+      <c r="X11" s="3" t="n">
         <v>30.9</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>97.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>0.8</v>
@@ -1420,7 +1424,7 @@
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>8.5</v>
+        <v>84.5</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>18</v>
@@ -1441,18 +1445,18 @@
         <v>19.3</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>61.1</v>
+        <v>21.5</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="R12" s="8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1462,13 +1466,13 @@
         <v>85.40000000000001</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>5.3</v>
+        <v>53.3</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>24.7</v>
+        <v>4.4</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>30.4</v>
@@ -1477,7 +1481,7 @@
         <v>97.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1493,7 +1497,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>256.7</v>
+        <v>356.1</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>31.1</v>
@@ -1508,7 +1512,7 @@
         <v>11.3</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.6</v>
+        <v>12.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.5</v>
@@ -1517,7 +1521,7 @@
         <v>2.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>20</v>
@@ -1526,22 +1530,22 @@
         <v>18.8</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>21.5</v>
+        <v>20.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>32.7</v>
+      <c r="S13" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>83.59999999999999</v>
@@ -1549,17 +1553,17 @@
       <c r="U13" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V13" s="8" t="n">
+      <c r="V13" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>93.8</v>
+        <v>43.2</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>44.4</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.2</v>
@@ -1578,22 +1582,22 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>374</v>
+        <v>340.8</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>32.5</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>19.6</v>
+        <v>12.6</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>12.9</v>
+      <c r="G14" s="8" t="n">
+        <v>22.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>2.8</v>
@@ -1602,16 +1606,16 @@
         <v>3.3</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>19.8</v>
+        <v>57.2</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>29.8</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>18.7</v>
+        <v>18.2</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>89.90000000000001</v>
@@ -1623,10 +1627,10 @@
         <v>30.6</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>22.6</v>
+        <v>2.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>50.9</v>
@@ -1644,7 +1648,7 @@
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>1.8</v>
@@ -1666,13 +1670,13 @@
         <v>433.5</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>29.5</v>
+        <v>9.5</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>20.2</v>
+        <v>41.8</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>24.9</v>
+        <v>44.1</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9.300000000000001</v>
@@ -1687,16 +1691,16 @@
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>20.4</v>
+        <v>26.4</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N15" s="8" t="n">
-        <v>20.8</v>
+        <v>0.9</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>11.3</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>88.8</v>
@@ -1720,19 +1724,19 @@
         <v>14.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>24.5</v>
+        <v>4.5</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>74</v>
+        <v>11.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1748,13 +1752,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1992.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>149.9</v>
+        <v>7.8</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>929.1</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>124.7</v>
@@ -1775,47 +1779,49 @@
         <v>6</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>100.9</v>
+        <v>160.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>918.6</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>94.59999999999999</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>21122.2</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>0.4</v>
+        <v>11.1</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>12.9</v>
+        <v>8.9</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>83</v>
+        <v>23.7</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>445.1</v>
+        <v>42.5</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>368.7</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>53.1</v>
+        <v>533.4</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>120.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>451.1</v>
+        <v>46.4</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>315.1</v>
+        <v>7.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>455.1</v>
+        <v>45.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1830,8 +1836,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>399.2</v>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+3986
+</t>
+        </is>
       </c>
       <c r="D17" s="3" t="n">
         <v>30</v>
@@ -1840,19 +1850,19 @@
         <v>19.8</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>24.9</v>
+        <v>14.4</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10.2</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>18.1</v>
+        <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n">
@@ -1862,7 +1872,7 @@
         <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>88.8</v>
@@ -1874,30 +1884,32 @@
         <v>28.6</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>24.6</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>28.5</v>
+        <v>22.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>73.7</v>
+        <v>3.7</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>42.8</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>43.2</v>
+        <v>23</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="Z17" s="3" t="n"/>
+        <v>1.9</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1912,58 +1924,58 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>137.3</v>
+        <v>43.2</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>30.8</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>19.4</v>
+        <v>12</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>24.9</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>81.8</v>
+        <v>11.2</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>17.7</v>
+        <v>12.7</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>21.9</v>
+        <v>82</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>42.9</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.2</v>
+        <v>23.1</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>6.1</v>
+        <v>63.1</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>4.4</v>
@@ -1978,10 +1990,14 @@
         <v>31</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>2.6</v>
+        <v>24.1</v>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+8 179
+</t>
+        </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2009,9 +2025,9 @@
         <v>25.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H19" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="I19" s="3" t="n">
@@ -2021,16 +2037,16 @@
         <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>21.5</v>
+        <v>0.8</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>87.5</v>
@@ -2042,7 +2058,7 @@
         <v>31.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>94.2</v>
+        <v>24.2</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>25.3</v>
@@ -2054,19 +2070,27 @@
         <v>21.7</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>25.8</v>
+        <v>85.8</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y19" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z19" s="3" t="n">
-        <v>6.2</v>
+        <v>2</v>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+44
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+818
+</t>
+        </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2082,34 +2106,39 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>256.8</v>
+        <v>3561.5</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>41.3</v>
+        <v>22.2</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>19.2</v>
+        <v>19.8</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>13.5</v>
+        <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+1 8 4
+7
+</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>18.8</v>
@@ -2118,13 +2147,13 @@
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>89</v>
+        <v>21.1</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>25.5</v>
+        <v>6.5</v>
+      </c>
+      <c r="Q20" s="8" t="n">
+        <v>535.2</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.5</v>
@@ -2133,7 +2162,7 @@
         <v>23.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>70.7</v>
+        <v>20.8</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>9.5</v>
@@ -2145,10 +2174,10 @@
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>67.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="Z20" s="3" t="n"/>
       <c r="AA20" s="3" t="inlineStr">
@@ -2168,7 +2197,7 @@
         <v>433.5</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18.4</v>
@@ -2176,11 +2205,9 @@
       <c r="F21" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="G21" s="3" t="n"/>
       <c r="H21" s="3" t="n">
-        <v>17.4</v>
+        <v>12.4</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>2.2</v>
@@ -2189,13 +2216,13 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>11.3</v>
+        <v>18.3</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>18.8</v>
@@ -2210,28 +2237,32 @@
         <v>30.1</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>21.7</v>
+        <v>41.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
+        <v>531</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>24.3</v>
+        <v>44.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>955.9</v>
+        <v>2.4</v>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+8111
+</t>
+        </is>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>250.4</v>
+        <v>850.1</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>4.5</v>
@@ -2250,22 +2281,22 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>374</v>
+        <v>34</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>34.8</v>
+        <v>31.2</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>24.5</v>
+        <v>84.5</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>15.3</v>
+        <v>0.2</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.1</v>
@@ -2277,16 +2308,16 @@
         <v>3.7</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>17.6</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>87.5</v>
+        <v>1.5</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>87</v>
+        <v>872</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>2.6</v>
@@ -2301,22 +2332,22 @@
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>56.4</v>
+        <v>568.1</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>21.6</v>
+        <v>4.6</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>85.5</v>
+        <v>5.5</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>3.6</v>
@@ -2335,76 +2366,76 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>374</v>
+        <v>1985.5</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>34.8</v>
+        <v>653.4</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>17.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>24.5</v>
+        <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>14.6</v>
+        <v>60.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>15.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.1</v>
+        <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>3.5</v>
+        <v>15.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>3.7</v>
+        <v>49.2</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>17.6</v>
+        <v>95.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>16.2</v>
+        <v>882.6</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>96.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>87</v>
+        <v>438.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>146.9</v>
+        <v>146.2</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>215.4</v>
+        <v>2952.6</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>462.1</v>
+        <v>12.8</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>103.6</v>
+        <v>10.7</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>28.7</v>
+        <v>26.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>411</v>
+        <v>0.4</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2420,76 +2451,74 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1925.5</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>53.1</v>
+        <v>5851.1</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>30.6</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>23</v>
+        <v>18.6</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>60.3</v>
+        <v>3.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>85</v>
+        <v>12.6</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>11.6</v>
+        <v>2.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>49.2</v>
-      </c>
+        <v>3.1</v>
+      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="n">
-        <v>95.2</v>
+        <v>19</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>88.2</v>
+        <v>12.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>96.5</v>
+        <v>1.3</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>437.2</v>
+        <v>872.4</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q24" s="8" t="n">
-        <v>46.9</v>
+        <v>2.7</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>29.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>14.3</v>
+        <v>22.9</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>19</v>
+        <v>23.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>215.4</v>
+        <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>462.1</v>
+        <v>4.4</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>103.6</v>
+        <v>22.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>28.7</v>
+        <v>0.9</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>411</v>
+        <v>0.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>7.1</v>
+        <v>0.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2505,76 +2534,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>385.1</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>30.6</v>
+        <v>34</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>26.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>816.1</v>
+        <v>13.3</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>24.6</v>
+        <v>45.1</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>12</v>
+        <v>0.1</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>87</v>
+        <v>18.8</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>19.3</v>
+        <v>0.1</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>60.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>21.7</v>
+        <v>0.5</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>29.2</v>
+        <v>324.3</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>22.9</v>
+        <v>24.3</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>23.8</v>
+        <v>1.8</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>59</v>
+        <v>56.9</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>17</v>
+        <v>19.7</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>24.4</v>
+        <v>7.1</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>22.1</v>
+        <v>20.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>85.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2590,49 +2619,49 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>374</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>34.1</v>
+        <v>34</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>26.1</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>19.3</v>
+        <v>13.3</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>13.1</v>
+        <v>45.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>12.8</v>
+        <v>0.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>31.6</v>
+        <v>36.3</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.4</v>
+        <v>7.5</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>20.4</v>
+        <v>18.1</v>
+      </c>
+      <c r="N26" s="8" t="n">
+        <v>60.4</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>31.3</v>
+        <v>324.3</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>24.3</v>
@@ -2647,19 +2676,19 @@
         <v>19.7</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>0.4</v>
+        <v>24.2</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>22.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>74.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2675,7 +2704,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>329.8</v>
+        <v>381.2</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>30.8</v>
@@ -2684,19 +2713,19 @@
         <v>18.6</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>24.7</v>
+        <v>24.2</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>31.6</v>
+        <v>2.6</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0.3</v>
@@ -2705,18 +2734,18 @@
         <v>19</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>18.4</v>
+        <v>12.6</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>87</v>
+        <v>87.2</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Q27" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q27" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2726,16 +2755,16 @@
         <v>24.5</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>24.2</v>
+        <v>6.1</v>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v>42.6</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>21.8</v>
+        <v>41.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>24.6</v>
@@ -2743,8 +2772,12 @@
       <c r="Y27" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="Z27" s="3" t="n">
-        <v>7.6</v>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+54
+</t>
+        </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2760,10 +2793,10 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>354.5</v>
+        <v>354.2</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.2</v>
+        <v>28.4</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>19.4</v>
@@ -2772,34 +2805,34 @@
         <v>23.8</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>17.8</v>
+        <v>12.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>5.3</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>20.2</v>
+        <v>10.2</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>17.6</v>
+        <v>18.8</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>20.8</v>
+        <v>61.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>187.5</v>
+        <v>82.5</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>26</v>
@@ -2808,7 +2841,7 @@
         <v>21.6</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>68.40000000000001</v>
@@ -2817,19 +2850,19 @@
         <v>10.6</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>23.2</v>
+        <v>63.5</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>20.8</v>
+        <v>6.2</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>808.1</v>
+        <v>8.1</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2848,10 +2881,10 @@
         <v>389.3</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>29.8</v>
+        <v>1.2</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>20.2</v>
+        <v>0.2</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>25</v>
@@ -2860,31 +2893,31 @@
         <v>9.6</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>19.6</v>
+        <v>3.8</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>239.6</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>18.8</v>
+        <v>19.2</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>21.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>28.2</v>
@@ -2899,22 +2932,22 @@
         <v>64.90000000000001</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>13.4</v>
+        <v>1.4</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>26</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="X29" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="X29" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2930,13 +2963,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>408.5</v>
+        <v>42.6</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>29.4</v>
+        <v>494.5</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>20.3</v>
+        <v>61.3</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>24.9</v>
@@ -2945,22 +2978,22 @@
         <v>9.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>20.1</v>
+        <v>4.1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.2</v>
+        <v>20.2</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>21.5</v>
@@ -2969,7 +3002,7 @@
         <v>90</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>12.9</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>28.6</v>
@@ -2984,10 +3017,10 @@
         <v>62.6</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>114.6</v>
+        <v>14.6</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>15.5</v>
+        <v>85.5</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>23</v>
@@ -2996,10 +3029,10 @@
         <v>26.5</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>6.1</v>
+        <v>2.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3015,10 +3048,10 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>50.3</v>
+        <v>2.3</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>97.8</v>
@@ -3027,49 +3060,49 @@
         <v>24.1</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>52.5</v>
+        <v>5.5</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>11.7</v>
+        <v>10</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.9</v>
+        <v>15.8</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>954.4</v>
+        <v>25.4</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N31" s="8" t="n">
-        <v>3.2</v>
+        <v>93.2</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>113.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>441.9</v>
+        <v>44.4</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>2.3</v>
+        <v>13.1</v>
       </c>
       <c r="Q31" s="8" t="n">
-        <v>138.5</v>
+        <v>38.5</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>43.8</v>
+        <v>3.7</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>22.7</v>
+        <v>18.7</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>332.8</v>
+        <v>334.8</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>64.3</v>
+        <v>0.5</v>
       </c>
       <c r="V31" s="8" t="n">
         <v>23.1</v>
@@ -3081,10 +3114,10 @@
         <v>24.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>399.8</v>
+        <v>322.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3100,46 +3133,48 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>371.3</v>
+        <v>437.3</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>30.1</v>
+        <v>0.4</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>19.6</v>
+        <v>2.6</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>10.1</v>
+        <v>2</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
+        <v>3.2</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="L32" s="3" t="n">
-        <v>19.9</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>92.2</v>
+        <v>18.5</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>206.1</v>
+        <v>26.6</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Q32" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q32" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3149,25 +3184,29 @@
         <v>24.5</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>122.1</v>
+        <v>12.9</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>24.6</v>
+        <v>4.6</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>22</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>24.9</v>
+        <v>42.9</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>6.5</v>
+        <v>22.8</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+78
+</t>
+        </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3183,52 +3222,52 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>437.3</v>
+        <v>3272</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>32.8</v>
+        <v>34.8</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>265.1</v>
+        <v>26.5</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>6.6</v>
+        <v>12.6</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>20.6</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>18.6</v>
+        <v>19.3</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>21.5</v>
+        <v>61.5</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>28.4</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>31</v>
+        <v>0.1</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>25.4</v>
@@ -3240,19 +3279,19 @@
         <v>19.5</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>28.2</v>
+        <v>25.8</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>23.7</v>
+        <v>2.8</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>26.4</v>
+        <v>5.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3268,7 +3307,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>397</v>
+        <v>36.6</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.3</v>
@@ -3277,19 +3316,19 @@
         <v>19.8</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>26.7</v>
+        <v>26.2</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>17.9</v>
+        <v>12.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
@@ -3298,46 +3337,50 @@
         <v>20.9</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>21.7</v>
+        <v>21.2</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>32.9</v>
+        <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>23.9</v>
+        <v>2.2</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>23.9</v>
+        <v>26.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>47.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>26.1</v>
+        <v>2.2</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>25.8</v>
+        <v>45.5</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>61.2</v>
+        <v>23.3</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>25.8</v>
+        <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v>7.4</v>
+        <v>83.2</v>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+5
+</t>
+        </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3353,76 +3396,74 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>362.4</v>
+        <v>884.5</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>30.4</v>
+        <v>24.6</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>20.2</v>
+        <v>20.7</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>25.3</v>
+        <v>22.7</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>10.2</v>
+        <v>3.4</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I35" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="J35" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>0</v>
+      <c r="K35" s="8" t="n">
+        <v>98</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>20.4</v>
+        <v>24.1</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>21</v>
+        <v>61.3</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>87.3</v>
+        <v>25.4</v>
       </c>
       <c r="P35" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="U35" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q35" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>25.5</v>
+      <c r="V35" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>23.3</v>
+        <v>20.3</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>27.2</v>
+        <v>2.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>83.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3438,76 +3479,74 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>398.9</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>24.6</v>
+        <v>28.6</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>22.7</v>
+        <v>24.3</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>3.9</v>
+        <v>8.6</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J36" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>289</v>
+      </c>
+      <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>2.9</v>
-      </c>
       <c r="Q36" s="3" t="n">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>21.2</v>
+        <v>23.1</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>24.3</v>
+        <v>25.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>88.5</v>
+        <v>72.3</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>3.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v>20.3</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="W36" s="3" t="n"/>
       <c r="X36" s="3" t="n">
-        <v>22.9</v>
+        <v>24.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>88.5</v>
+        <v>326.6</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3523,76 +3562,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>398.9</v>
+        <v>1683.5</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>126.4</v>
+        <v>56.1</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>24.3</v>
+        <v>35.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>8.6</v>
+        <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>19</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.4</v>
+        <v>15.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>9</v>
+        <v>16.2</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>120.6</v>
+        <v>103.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>19.3</v>
+        <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>21.7</v>
+        <v>117.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>89</v>
+        <v>432.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>27</v>
+        <v>691.6</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>23.1</v>
+        <v>6.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>25.8</v>
+        <v>62.7</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>72.3</v>
+        <v>13.1</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>651.5</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>25</v>
+        <v>126.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>22.1</v>
+        <v>76.2</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>24.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>0.6</v>
+        <v>62.9</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3608,76 +3647,76 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1683.5</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>2.9</v>
+        <v>336.7</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>64.59999999999999</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>55.1</v>
+        <v>25.1</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>82.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>163.5</v>
+        <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>7.8</v>
+        <v>19.5</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>44.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>437.5</v>
+        <v>87.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>399.6</v>
+        <v>3</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="S38" s="8" t="n">
-        <v>620.1</v>
+        <v>23.1</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>343.7</v>
+        <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>65.7</v>
+        <v>13.1</v>
       </c>
       <c r="V38" s="8" t="n">
-        <v>26.1</v>
+        <v>52.6</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>44.4</v>
+        <v>0.1</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>4.4</v>
+        <v>35.4</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>396.6</v>
+        <v>0.1</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3693,76 +3732,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>336.7</v>
+        <v>42.7</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>30</v>
+        <v>31.8</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>20.2</v>
+        <v>19.5</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>25.1</v>
+        <v>25.7</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>12.6</v>
+        <v>15.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>15.7</v>
+        <v>3.4</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>25.1</v>
+        <v>41.5</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>22</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>87.5</v>
+        <v>2.4</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>14.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>25.2</v>
+        <v>31.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>68.7</v>
+        <v>54.5</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>18.1</v>
+        <v>19.8</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>95.2</v>
+        <v>76.8</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>22.4</v>
+        <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>25.4</v>
+        <v>22.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>79.3</v>
+        <v>85.5</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3778,76 +3817,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>48.4</v>
+        <v>4.4</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>19.5</v>
+        <v>24.1</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>2.4</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>25.7</v>
+        <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>13.3</v>
+        <v>3.9</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>2.5</v>
+        <v>19</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>6.4</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.1</v>
+        <v>4.9</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>0.1</v>
+        <v>22.1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>88</v>
+        <v>88.8</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>2.7</v>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>23.1</v>
+        <v>19.8</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>23.6</v>
+        <v>22.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>54.5</v>
+        <v>89.7</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.2</v>
+        <v>2.6</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>26.8</v>
+        <v>21.3</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>77.8</v>
+        <v>1.6</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>25.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3863,76 +3902,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>48.8</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>24.1</v>
+        <v>29.4</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>20.2</v>
+        <v>13.5</v>
       </c>
       <c r="F41" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="N41" s="8" t="n">
+      <c r="Y41" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="O41" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="U41" s="3" t="n">
+      <c r="Z41" s="3" t="n">
         <v>2.6</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>3.6</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3947,77 +3986,81 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>448.8</v>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">442
+2 6
+</t>
+        </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>11.4</v>
+        <v>33.1</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>17.4</v>
+        <v>25.8</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>25.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>10.4</v>
+        <v>4.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>19.9</v>
+        <v>12.2</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>19.1</v>
+        <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>20.8</v>
+        <v>12.6</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>12.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>28</v>
+        <v>24.7</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>21.6</v>
+        <v>22.3</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>21.7</v>
+        <v>25.4</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>58.4</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>16.1</v>
+        <v>5.2</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>24.6</v>
+        <v>63.2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>25.2</v>
+        <v>24.4</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>81.3</v>
+        <v>82</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>2.6</v>
+        <v>6.1</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4033,76 +4076,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>4.4</v>
+        <v>341.3</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>32.8</v>
+        <v>32.1</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>17</v>
+        <v>18.6</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>15.3</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>25.8</v>
+        <v>13.4</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>15.6</v>
+        <v>16.9</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L43" s="8" t="n">
-        <v>78.09999999999999</v>
+        <v>15.2</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>16.1</v>
+        <v>17.7</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>17.6</v>
+        <v>19.4</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>89</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q43" s="8" t="n">
-        <v>30.8</v>
+        <v>2.4</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>22.6</v>
+        <v>66.3</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>22.2</v>
+        <v>12.3</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>50</v>
+        <v>21.1</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>23</v>
+        <v>6.3</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>21.4</v>
+        <v>61.1</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>87</v>
+        <v>0.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>0.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4118,76 +4161,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>341.3</v>
+        <v>141.6</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="E44" s="8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>16.9</v>
-      </c>
       <c r="I44" s="3" t="n">
-        <v>2.2</v>
+        <v>82.8</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>15.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>19</v>
+        <v>0.1</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>17.7</v>
+        <v>19.5</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>22.6</v>
+        <v>3.3</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="S44" s="8" t="n">
-        <v>22.3</v>
+        <v>2.2</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>92.3</v>
+        <v>3.2</v>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v>33.5</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>20.2</v>
+        <v>21.8</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>4.6</v>
+        <v>73.8</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4202,73 +4245,79 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>141.6</v>
-      </c>
+      <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="n">
-        <v>23.9</v>
+        <v>22.2</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>19</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F45" s="3" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>1825.6</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R45" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P45" s="3" t="n"/>
-      <c r="Q45" s="3" t="n"/>
-      <c r="R45" s="3" t="n">
-        <v>2.4</v>
-      </c>
       <c r="S45" s="3" t="n">
-        <v>22</v>
+        <v>22.9</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>7.4</v>
+        <v>69</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>7.2</v>
+        <v>11.9</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>455.1</v>
+        <v>242.4</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>7.1</v>
+        <v>21.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y45" s="3" t="n">
-        <v>81.5</v>
+        <v>124.2</v>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 7
+57
+</t>
+        </is>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4284,43 +4333,46 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>311.7</v>
+        <v>5.3</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.1</v>
+        <v>29</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>240.1</v>
+        <v>18.9</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>48</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="I46" s="8" t="n">
-        <v>13.3</v>
+        <v>1.1</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>16.6</v>
+        <v>2.8</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>30</v>
+        <v>1.8</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>3.4</v>
+        <v>19.4</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>825.6</v>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20 8
+</t>
+        </is>
       </c>
       <c r="O46" s="3" t="n">
-        <v>324.1</v>
+        <v>89</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>2.4</v>
@@ -4329,29 +4381,31 @@
         <v>26.2</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>22.9</v>
-      </c>
+        <v>21.5</v>
+      </c>
+      <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n">
         <v>69</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="8" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="W46" s="3" t="n"/>
+      <c r="X46" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="Y46" s="3" t="n"/>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 7
+57
+</t>
+        </is>
+      </c>
       <c r="Z46" s="3" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,75 +736,69 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>21.2</v>
+        <v>9437.5</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>31.2</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1.3</v>
+        <v>14.1</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>24.2</v>
+        <v>0.4</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>22.4</v>
+        <v>142.1</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K4" s="3" t="n"/>
+        <v>14.2</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>17.5</v>
+      <c r="N4" s="8" t="n">
+        <v>82.5</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>87</v>
+        <v>187</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q4" s="8" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R4" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="R4" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="S4" s="3" t="n">
-        <v>27.8</v>
+      <c r="S4" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>63.7</v>
+        <v>631.1</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>22.2</v>
+        <v>18.1</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X4" s="3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -818,29 +812,25 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="D5" s="3" t="n">
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="F5" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F5" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>57.2</v>
+        <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0.4</v>
+        <v>11.6</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="8" t="n">
+        <v>87.40000000000001</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>25.8</v>
@@ -849,46 +839,42 @@
         <v>19.1</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N5" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N5" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>24.3</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="S5" s="3" t="n">
+      <c r="S5" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>82.8</v>
+        <v>187.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>4.2</v>
+        <v>12.9</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>18.9</v>
-      </c>
+        <v>20.6</v>
+      </c>
+      <c r="W5" s="3" t="inlineStr"/>
       <c r="X5" s="3" t="n">
-        <v>20.7</v>
+        <v>27.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>35</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>3.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -904,9 +890,9 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>431.6</v>
-      </c>
-      <c r="D6" s="3" t="n">
+        <v>432.4</v>
+      </c>
+      <c r="D6" s="8" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" s="3" t="n">
@@ -916,64 +902,62 @@
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>3.6</v>
-      </c>
       <c r="K6" s="3" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>12</v>
+      <c r="M6" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>188.6</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q6" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="Q6" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="3" t="n">
-        <v>23.9</v>
+      <c r="R6" s="8" t="n">
+        <v>232.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>25.9</v>
+        <v>651.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>61.9</v>
+        <v>1608.9</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>26.5</v>
+        <v>20.7</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>11.1</v>
+        <v>185</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>2.5</v>
+        <v>13.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -989,76 +973,74 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="D7" s="3" t="n">
+        <v>1437.3</v>
+      </c>
+      <c r="D7" s="8" t="n">
         <v>33</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G7" s="3" t="n">
+        <v>251.1</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>17.3</v>
+      <c r="N7" s="8" t="n">
+        <v>67.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>187.6</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" s="8" t="n">
-        <v>18.9</v>
+      <c r="Q7" s="3" t="n">
+        <v>31.9</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="S7" s="3" t="n">
+      <c r="S7" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>5.1</v>
+        <v>2022.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W7" s="3" t="n">
+      <c r="V7" s="8" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="W7" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="X7" s="3" t="n">
-        <v>2.8</v>
+      <c r="X7" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>5.2</v>
+        <v>177.9</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1074,61 +1056,61 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.4</v>
+        <v>1297.2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>52.6</v>
+        <v>32.6</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>86.2</v>
+        <v>19.8</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>26.2</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.2</v>
+        <v>17.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>4.4</v>
+        <v>16.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K8" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="L8" s="3" t="n">
+      <c r="K8" s="8" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="L8" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>865.6</v>
-      </c>
-      <c r="N8" s="3" t="n">
+      <c r="M8" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="N8" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>82.7</v>
+        <v>187.7</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q8" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="Q8" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="S8" s="3" t="n">
+      <c r="S8" s="8" t="n">
         <v>33.2</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>2524.1</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>24</v>
@@ -1136,14 +1118,14 @@
       <c r="W8" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X8" s="3" t="n">
-        <v>22</v>
+      <c r="X8" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>96.2</v>
+        <v>90.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1159,24 +1141,20 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>6.6</v>
+        <v>1666.5</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="F9" s="3" t="n"/>
+        <v>852.6</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="n">
-        <v>611.1</v>
+        <v>681.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>80.5</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
@@ -1184,49 +1162,43 @@
         <v>44.3</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>94.3</v>
+        <v>194.3</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>82.8</v>
+        <v>187.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>96.3</v>
+        <v>196.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>440.9</v>
+        <v>1440.9</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>12.9</v>
+        <v>162.9</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>138.8</v>
+        <v>1138.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>11.3</v>
+        <v>1617.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>31.9</v>
+        <v>132.9</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>360.9</v>
+        <v>1360.9</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>126.1</v>
-      </c>
-      <c r="W9" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>1126.1</v>
+      </c>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="inlineStr"/>
       <c r="Z9" s="3" t="n">
-        <v>2.8</v>
+        <v>32.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1242,76 +1214,72 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>333.2</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>30.5</v>
+        <v>333.3</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>5.1</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>18.5</v>
+        <v>185.1</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>1.6</v>
+        <v>12</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>16.1</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="L10" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="M10" s="8" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="n">
-        <v>88.2</v>
+        <v>188.2</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="R10" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="R10" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="S10" s="3" t="n">
-        <v>2.6</v>
+      <c r="S10" s="8" t="n">
+        <v>26.4</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>2.2</v>
+        <v>272.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>0.4</v>
+        <v>11.7</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>25.8</v>
+        <v>0.5</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>2.6</v>
+        <v>22.6</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>806.5</v>
+        <v>180.5</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>6.6</v>
+        <v>16.6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1327,77 +1295,73 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>445.6</v>
+        <v>1445</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="F11" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>18.8</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3.3</v>
+        <v>13.3</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="3" t="n">
-        <v>20.1</v>
-      </c>
+      <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="N11" s="3" t="n">
-        <v>10.7</v>
+      <c r="N11" s="8" t="n">
+        <v>20.7</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>187.9</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>27.9</v>
+        <v>41.9</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="S11" s="3" t="n">
-        <v>31.9</v>
+      <c r="S11" s="8" t="n">
+        <v>981.9</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="U11" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="V11" s="3" t="n">
+      <c r="U11" s="8" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="V11" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.9</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>197.5</v>
+      </c>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1420,26 +1384,26 @@
       <c r="E12" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>84.5</v>
+        <v>18.5</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.9</v>
+        <v>12.9</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>20.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>19.3</v>
@@ -1451,10 +1415,10 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>22.7</v>
+        <v>20.7</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>72.2</v>
+        <v>27.8</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>25.2</v>
@@ -1463,25 +1427,25 @@
         <v>30.8</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>8544.1</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="V12" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X12" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>284.4</v>
+      </c>
+      <c r="X12" s="8" t="n">
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>97.7</v>
+        <v>197.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>0.8</v>
+        <v>10.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1497,9 +1461,9 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>356.1</v>
-      </c>
-      <c r="D13" s="3" t="n">
+        <v>39356.7</v>
+      </c>
+      <c r="D13" s="8" t="n">
         <v>31.1</v>
       </c>
       <c r="E13" s="3" t="n">
@@ -1511,19 +1475,19 @@
       <c r="G13" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H13" s="3" t="n">
-        <v>12.6</v>
+      <c r="H13" s="8" t="n">
+        <v>17.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L13" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="L13" s="8" t="n">
         <v>20</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1533,40 +1497,38 @@
         <v>20.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>2.5</v>
-      </c>
+        <v>189.1</v>
+      </c>
+      <c r="P13" s="3" t="inlineStr"/>
       <c r="Q13" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="S13" s="8" t="n">
-        <v>24.7</v>
+      <c r="S13" s="3" t="n">
+        <v>32.7</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="U13" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="V13" s="3" t="n">
+      <c r="U13" s="8" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="V13" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="3" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="X13" s="3" t="n">
+      <c r="W13" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X13" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>44.4</v>
+        <v>197.7</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>2.2</v>
+        <v>10.7</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1582,43 +1544,41 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>340.8</v>
-      </c>
-      <c r="D14" s="3" t="n">
+        <v>13974</v>
+      </c>
+      <c r="D14" s="8" t="n">
         <v>32.5</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>12.6</v>
+        <v>19.6</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="G14" s="8" t="n">
-        <v>22.9</v>
+      <c r="G14" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>12.2</v>
+        <v>17.2</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>3.3</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>57.2</v>
+        <v>5.7</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>189.9</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>2.3</v>
@@ -1627,10 +1587,10 @@
         <v>30.6</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>2.6</v>
+        <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>2.3</v>
+        <v>22.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>50.9</v>
@@ -1644,11 +1604,11 @@
       <c r="W14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="3" t="n">
+      <c r="X14" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>1.8</v>
@@ -1670,40 +1630,38 @@
         <v>433.5</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>44.1</v>
+        <v>29.5</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>24.9</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="H15" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H15" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>26.4</v>
+        <v>20.4</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="N15" s="3" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>88.8</v>
+        <v>188.8</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>2.6</v>
@@ -1714,29 +1672,29 @@
       <c r="R15" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S15" s="3" t="n">
+      <c r="S15" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>63.8</v>
+        <v>163.8</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="V15" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>21.1</v>
+      <c r="V15" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="W15" s="8" t="n">
+        <v>241.1</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>2.8</v>
+        <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>11.5</v>
+        <v>174</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>7.2</v>
+        <v>17.9</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1752,76 +1710,70 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>11992.8</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>7.8</v>
+        <v>149.9</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>929.1</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>124.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>50.8</v>
+        <v>150.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>11.1</v>
-      </c>
+        <v>190.3</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>160.9</v>
+        <v>1100.9</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>21122.2</v>
+        <v>105.2</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>11.1</v>
+        <v>444.1</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>8.9</v>
+        <v>12.9</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>142.8</v>
+        <v>1142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>23.7</v>
+        <v>123</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>42.5</v>
+        <v>142.5</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>368.7</v>
+        <v>1368.7</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>533.4</v>
+        <v>533441.5</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="3" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>7.3</v>
-      </c>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>45.1</v>
+        <v>1455.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>3.4</v>
+        <v>13.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1836,12 +1788,8 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-3986
-</t>
-        </is>
+      <c r="C17" s="3" t="n">
+        <v>39.9</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>30</v>
@@ -1849,66 +1797,66 @@
       <c r="E17" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>14.4</v>
+      <c r="F17" s="8" t="n">
+        <v>224.9</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>2.2</v>
+        <v>18.1</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>81.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>1</v>
+      <c r="N17" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>88.8</v>
+        <v>188.8</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="3" t="n">
-        <v>28.6</v>
+      <c r="Q17" s="8" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>22.5</v>
+        <v>946.4</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>6.6</v>
+        <v>173.7</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>10.6</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>42.8</v>
+        <v>24.2</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>23</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>2.5</v>
+        <v>27.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>1.9</v>
+        <v>191</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>2.7</v>
+        <v>12.7</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1924,31 +1872,29 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>43.2</v>
+        <v>437.5</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>30.8</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>3.5</v>
+        <v>19</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="8" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>39.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.6</v>
+        <v>18</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>19.2</v>
@@ -1960,44 +1906,40 @@
         <v>19.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="P18" s="8" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="Q18" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Q18" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S18" s="3" t="n">
+      <c r="S18" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>63.1</v>
+        <v>163.1</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V18" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V18" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>31</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="Z18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-8 179
-</t>
-        </is>
+        <v>92.09999999999999</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2013,7 +1955,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>423.9</v>
+        <v>1423.9</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>32.5</v>
@@ -2021,38 +1963,38 @@
       <c r="E19" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>14.2</v>
+      <c r="G19" s="8" t="n">
+        <v>124.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.9</v>
+        <v>16.1</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.3</v>
+        <v>13.5</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.8</v>
+        <v>28.5</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>18.2</v>
+      <c r="M19" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>87.5</v>
+        <v>2.3</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>31.8</v>
@@ -2064,33 +2006,25 @@
         <v>25.3</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>54</v>
+        <v>62.1</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="3" t="n">
-        <v>85.8</v>
+      <c r="V19" s="8" t="n">
+        <v>25.8</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-44
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-818
-</t>
-        </is>
+      <c r="X19" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y19" s="3" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2106,80 +2040,77 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3561.5</v>
+        <v>256.8</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>22.2</v>
+        <v>27.2</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-1 8 4
-7
-</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>82.8</v>
+        <v>17.4</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="M20" s="3" t="n">
+      <c r="K20" s="8" t="n">
+        <v>2408</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="M20" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>21.1</v>
+        <v>189</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q20" s="8" t="n">
-        <v>535.2</v>
-      </c>
-      <c r="R20" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R20" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>20.8</v>
+        <v>70.7</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>9.5</v>
+        <v>19.5</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="3" t="n">
+      <c r="W20" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>2.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+        <v>167.2</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2194,10 +2125,10 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>433.5</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>30.2</v>
+        <v>1433.5</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>30.8</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18.4</v>
@@ -2205,67 +2136,61 @@
       <c r="F21" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="G21" s="3" t="n"/>
+      <c r="G21" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="H21" s="3" t="n">
-        <v>12.4</v>
+        <v>17.7</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>18.3</v>
+        <v>1.4</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q21" s="3" t="n">
+        <v>186.7</v>
+      </c>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="8" t="n">
         <v>30.1</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>41.7</v>
+        <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>531</v>
+        <v>151</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="V21" s="3" t="n">
-        <v>44.3</v>
+      <c r="V21" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-8111
-</t>
-        </is>
+        <v>2.2</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>25.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>850.1</v>
+        <v>185</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2281,46 +2206,46 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>34</v>
+        <v>374</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>31.2</v>
+        <v>31.8</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>12.2</v>
+        <v>17.2</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>84.5</v>
+        <v>24.5</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.2</v>
+        <v>15.5</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.1</v>
+        <v>21.1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3.7</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>12.5</v>
+        <v>17.6</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.5</v>
+        <v>17.5</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>872</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>2.6</v>
+        <v>187</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>30.2</v>
@@ -2328,26 +2253,26 @@
       <c r="R22" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="S22" s="3" t="n">
+      <c r="S22" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>568.1</v>
+        <v>156.4</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="3" t="n">
-        <v>21.8</v>
+      <c r="V22" s="8" t="n">
+        <v>21.2</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="X22" s="3" t="n">
-        <v>4.6</v>
+      <c r="X22" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>5.5</v>
+        <v>185.5</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>3.6</v>
@@ -2366,19 +2291,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1985.5</v>
+        <v>1925.5</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>653.4</v>
+        <v>153.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>123</v>
+        <v>1123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>60.3</v>
+        <v>160.3</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>85.59999999999999</v>
@@ -2387,55 +2312,47 @@
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>15.5</v>
+        <v>135.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>49.2</v>
+        <v>49.9</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>95.2</v>
+        <v>195.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>882.6</v>
+        <v>1882.8</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>96.5</v>
+        <v>196.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>438.2</v>
+        <v>1437.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v>146.2</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>4.3</v>
-      </c>
+        <v>13.7</v>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
       <c r="S23" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2952.6</v>
+        <v>1295.2</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="V23" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>10.7</v>
-      </c>
+        <v>85.2</v>
+      </c>
+      <c r="V23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="inlineStr"/>
       <c r="X23" s="3" t="n">
-        <v>26.7</v>
+        <v>1126.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>0.4</v>
+        <v>1411</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>2.1</v>
+        <v>27.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2451,7 +2368,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5851.1</v>
+        <v>385.1</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>30.6</v>
@@ -2459,14 +2376,14 @@
       <c r="E24" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F24" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>12.6</v>
+        <v>12</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>87.40000000000001</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2474,23 +2391,21 @@
       <c r="J24" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K24" s="3" t="n"/>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>1.3</v>
+      <c r="M24" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="N24" s="8" t="n">
+        <v>19.5</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>872.4</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q24" s="3" t="n">
+        <v>187.4</v>
+      </c>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="8" t="n">
         <v>29.2</v>
       </c>
       <c r="R24" s="3" t="n">
@@ -2500,25 +2415,25 @@
         <v>23.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>59</v>
+        <v>159</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>4.4</v>
+        <v>17.6</v>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v>24.4</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="X24" s="3" t="n">
-        <v>0.9</v>
+      <c r="X24" s="8" t="n">
+        <v>25.3</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>0.8</v>
+        <v>182.2</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2534,19 +2449,19 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>26.1</v>
+        <v>1374</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>32.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>45.1</v>
+        <v>19.3</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>25.7</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.1</v>
+        <v>9.1</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>18.8</v>
@@ -2555,55 +2470,53 @@
         <v>2.4</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>13.6</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr"/>
       <c r="L25" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>0.1</v>
+        <v>18.4</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>60.4</v>
+        <v>20.4</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>324.3</v>
+        <v>2.2</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>31.3</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>1.8</v>
+        <v>243.1</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>56.9</v>
+        <v>956.9</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W25" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="W25" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="3" t="n">
-        <v>66.09999999999999</v>
+      <c r="X25" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>74.8</v>
+        <v>1747.6</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2619,76 +2532,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>26.1</v>
+        <v>329.8</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>30.8</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>13.3</v>
+        <v>18.6</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>45.1</v>
+        <v>24.7</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>2.4</v>
+        <v>12.2</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>11.9</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>36.3</v>
+        <v>12.6</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>7.5</v>
+        <v>10.3</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>18.1</v>
+        <v>1.6</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>60.4</v>
+        <v>949.2</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>90</v>
+        <v>187</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>2.2</v>
+        <v>12.8</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>324.3</v>
+        <v>24.4</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>24.3</v>
+        <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>25.9</v>
+        <v>24.5</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>56.9</v>
+        <v>180</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V26" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V26" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>6.8</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>74.8</v>
+        <v>181.1</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.5</v>
+        <v>17.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2704,80 +2617,74 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>381.2</v>
+        <v>0.8</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>30.8</v>
+        <v>28.2</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>24.2</v>
+        <v>19.4</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12.8</v>
+        <v>18.8</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>2.6</v>
+        <v>17.8</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="8" t="n">
+        <v>21.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>19</v>
+        <v>5.3</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>19.2</v>
+        <v>18.8</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>87.2</v>
+        <v>187.5</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>24.4</v>
+        <v>21.9</v>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>24.5</v>
+        <v>23</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>86</v>
+        <v>168.4</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>6.1</v>
+        <v>10.6</v>
       </c>
       <c r="V27" s="8" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>24.6</v>
+        <v>23.2</v>
+      </c>
+      <c r="W27" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>23</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-54
-</t>
-        </is>
+        <v>180.8</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>5.4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2793,76 +2700,76 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>354.2</v>
+        <v>9389.299999999999</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>28.4</v>
+        <v>29.8</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>19.4</v>
+        <v>20.2</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>23.8</v>
+        <v>25</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>12.8</v>
+        <v>19.6</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>39.8</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>5.3</v>
+        <v>19.6</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>10.2</v>
+        <v>20.6</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>61.2</v>
+        <v>19.2</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>21.3</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>82.5</v>
+        <v>187.4</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="Q28" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="R28" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V28" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="R28" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>63.5</v>
-      </c>
       <c r="W28" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v>23</v>
+        <v>23.6</v>
+      </c>
+      <c r="X28" s="8" t="n">
+        <v>27.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>8.1</v>
+        <v>82</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2878,76 +2785,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>389.3</v>
+        <v>408.5</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.2</v>
+        <v>29.4</v>
       </c>
       <c r="E29" s="3" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K29" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K29" s="8" t="n">
-        <v>239.6</v>
-      </c>
       <c r="L29" s="3" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>28.2</v>
+        <v>21.3</v>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="3" t="n">
-        <v>24.8</v>
+      <c r="S29" s="8" t="n">
+        <v>226.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>162.6</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>26</v>
+        <v>14.6</v>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v>25.5</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>27.6</v>
+        <v>23</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>26.5</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>82</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>6.1</v>
+        <v>16.1</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2963,76 +2870,76 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>42.6</v>
+        <v>1856.4</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>494.5</v>
+        <v>150.3</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>61.3</v>
+        <v>97.8</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>24.9</v>
+        <v>124.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>9.1</v>
+        <v>152.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>4.1</v>
+        <v>191.9</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1</v>
+        <v>180</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2.9</v>
+        <v>15.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>20.2</v>
+        <v>125.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>20.3</v>
+        <v>199.6</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>19.5</v>
+        <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>21.5</v>
+        <v>1103.2</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>90</v>
+        <v>1441.9</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2.3</v>
+        <v>13.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>28.6</v>
+        <v>1138.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>23</v>
+        <v>1113.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>24.5</v>
+        <v>122.8</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>62.6</v>
+        <v>1332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>14.6</v>
+        <v>164.5</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>85.5</v>
+        <v>1823.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>23</v>
+        <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>26.5</v>
+        <v>1124.3</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>1399.8</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>2.6</v>
+        <v>32.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3048,76 +2955,74 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>11.4</v>
+        <v>383.1</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2.3</v>
+        <v>30.1</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>24.1</v>
+        <v>19.6</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>2.9</v>
+        <v>184.5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>25.4</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>19.9</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>93.2</v>
+        <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>113.6</v>
+        <v>6.4</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>44.4</v>
+        <v>188.4</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>13.1</v>
+        <v>12.6</v>
       </c>
       <c r="Q31" s="8" t="n">
-        <v>38.5</v>
+        <v>27.7</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>3.7</v>
+        <v>22.7</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>18.7</v>
+        <v>24.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>334.8</v>
+        <v>166.6</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>0.5</v>
+        <v>12.9</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>23.1</v>
+        <v>24.6</v>
       </c>
       <c r="W31" s="8" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="X31" s="8" t="n">
-        <v>24.3</v>
+        <v>22</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>94.90000000000001</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>322.8</v>
+        <v>80</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.2</v>
+        <v>6.5</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3136,77 +3041,69 @@
         <v>437.3</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>2.6</v>
+        <v>32.8</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>1.5</v>
-      </c>
+        <v>865.1</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2</v>
+        <v>13.5</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3.2</v>
+        <v>14.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>20.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>18.5</v>
+        <v>12.3</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>26.6</v>
+        <v>21.5</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>2.6</v>
-      </c>
+        <v>188.4</v>
+      </c>
+      <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="3" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>22.7</v>
+        <v>31</v>
+      </c>
+      <c r="R32" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>24.5</v>
+        <v>25.4</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>66.5</v>
+        <v>156.6</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>12.9</v>
+        <v>19.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>42.9</v>
+        <v>23.7</v>
+      </c>
+      <c r="X32" s="8" t="n">
+        <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-78
-</t>
-        </is>
+        <v>69.09999999999999</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>1118.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3222,76 +3119,74 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>3272</v>
+        <v>1397</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>20.2</v>
+        <v>33.7</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>26.5</v>
+        <v>26.7</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>12.6</v>
+        <v>34.1</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>18.2</v>
+        <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>4.3</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="3" t="n">
-        <v>0.8</v>
+        <v>10</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>20.9</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>19.3</v>
+        <v>49.5</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>61.5</v>
+        <v>26.7</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>28.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>0.1</v>
+        <v>3.1</v>
+      </c>
+      <c r="Q33" s="8" t="n">
+        <v>32.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>44</v>
+        <v>23.9</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>25.4</v>
+        <v>63.4</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="V33" s="3" t="n">
+        <v>1947.7</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="W33" s="3" t="n">
-        <v>2.8</v>
+      <c r="W33" s="8" t="n">
+        <v>22.8</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>5.8</v>
+        <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>2.6</v>
+        <v>127.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0.3</v>
+        <v>17.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3307,80 +3202,74 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>36.6</v>
+        <v>362.4</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.3</v>
+        <v>30.4</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>26.2</v>
+        <v>25.3</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>13.9</v>
+        <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I34" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="I34" s="3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="J34" s="3" t="n">
-        <v>5.5</v>
+        <v>12.6</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>2.9</v>
-      </c>
+        <v>187.3</v>
+      </c>
+      <c r="P34" s="3" t="inlineStr"/>
       <c r="Q34" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S34" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="S34" s="8" t="n">
         <v>26.6</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>2.2</v>
+        <v>17.2</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>45.5</v>
+        <v>55.4</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X34" s="3" t="n">
+      <c r="X34" s="8" t="n">
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-5
-</t>
-        </is>
+        <v>183.2</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3396,52 +3285,54 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>884.5</v>
-      </c>
-      <c r="D35" s="3" t="n">
+        <v>187.9</v>
+      </c>
+      <c r="D35" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>3.4</v>
+        <v>23.9</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="I35" s="3" t="n"/>
+      <c r="I35" s="3" t="n">
+        <v>10.3</v>
+      </c>
       <c r="J35" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K35" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>24.1</v>
+        <v>10.4</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N35" s="3" t="n">
-        <v>61.3</v>
+      <c r="N35" s="8" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>25.4</v>
+        <v>854.1</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q35" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Q35" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S35" s="3" t="n">
+      <c r="S35" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="T35" s="3" t="n">
@@ -3456,14 +3347,14 @@
       <c r="W35" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="X35" s="3" t="n">
+      <c r="X35" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="Z35" s="3" t="n">
         <v>2.9</v>
-      </c>
-      <c r="Y35" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>0.6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3481,17 +3372,17 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="F36" s="3" t="n">
+      <c r="E36" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>19</v>
@@ -3503,7 +3394,7 @@
         <v>2.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>20.6</v>
@@ -3511,23 +3402,23 @@
       <c r="M36" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>21.2</v>
+      <c r="N36" s="8" t="n">
+        <v>21.7</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>289</v>
+        <v>189</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="R36" s="3" t="n">
+      <c r="Q36" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="R36" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>25.8</v>
+      <c r="S36" s="8" t="n">
+        <v>593.8</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>72.3</v>
@@ -3535,18 +3426,20 @@
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="W36" s="3" t="n"/>
-      <c r="X36" s="3" t="n">
+      <c r="V36" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W36" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X36" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>326.6</v>
+        <v>178.2</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.4</v>
+        <v>16.9</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3562,22 +3455,16 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1683.5</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>35.5</v>
-      </c>
+        <v>11683.5</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="n">
         <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>192.4</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>12.6</v>
@@ -3586,52 +3473,44 @@
         <v>15.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>16.2</v>
+        <v>160.8</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="3" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>117.2</v>
-      </c>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="n">
-        <v>432.5</v>
+        <v>1432.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.9</v>
+        <v>14.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>691.6</v>
+        <v>139.6</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>6.4</v>
+        <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>62.7</v>
+        <v>126.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>13.1</v>
+        <v>3431.1</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>651.5</v>
+        <v>165.7</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>72.09999999999999</v>
-      </c>
+      <c r="W37" s="3" t="inlineStr"/>
+      <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>79.3</v>
+        <v>396.6</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>62.9</v>
+        <v>342.4</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3649,74 +3528,72 @@
       <c r="C38" s="3" t="n">
         <v>336.7</v>
       </c>
-      <c r="D38" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>64.59999999999999</v>
+      <c r="D38" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>25.1</v>
+        <v>5.4</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="H38" s="8" t="n">
-        <v>82.5</v>
+      <c r="H38" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>7.4</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>211.1</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>44.4</v>
+        <v>21.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>87.5</v>
+        <v>187.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>17.9</v>
+        <v>27.9</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S38" s="3" t="n">
+      <c r="S38" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>68.7</v>
+        <v>168.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>52.6</v>
+        <v>18.1</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>0.1</v>
+        <v>22.4</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>35.4</v>
+        <v>25.4</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>0.1</v>
+        <v>79.3</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>0.6</v>
+        <v>18.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3732,12 +3609,12 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>42.7</v>
+        <v>1400.8</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="F39" s="3" t="n">
@@ -3750,58 +3627,58 @@
         <v>18.1</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>15.5</v>
+        <v>52.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>41.5</v>
+        <v>10</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>20.5</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="3" t="n">
+      <c r="N39" s="8" t="n">
         <v>22</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>31.4</v>
+        <v>91</v>
+      </c>
+      <c r="P39" s="8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>30.4</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>31.6</v>
+        <v>23.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>54.5</v>
+        <v>345.1</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" s="3" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="W39" s="3" t="n">
+      <c r="V39" s="8" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="W39" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="X39" s="3" t="n">
-        <v>22.6</v>
+      <c r="X39" s="8" t="n">
+        <v>27.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>85.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.6</v>
+        <v>17.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3817,31 +3694,31 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>24.1</v>
+        <v>74.40000000000001</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>2.4</v>
+        <v>20.2</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H40" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H40" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="I40" s="8" t="n">
-        <v>6.4</v>
+      <c r="I40" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.5</v>
+        <v>10.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>4.9</v>
+        <v>14.9</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>20.4</v>
@@ -3850,16 +3727,16 @@
         <v>19.1</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>22.1</v>
+        <v>10.1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>88.8</v>
+        <v>88</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.7</v>
+        <v>18.7</v>
       </c>
       <c r="Q40" s="8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>19.8</v>
@@ -3868,7 +3745,7 @@
         <v>22.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>89.7</v>
+        <v>189.7</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>2.6</v>
@@ -3877,16 +3754,16 @@
         <v>21.3</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>21.2</v>
+        <v>19.6</v>
+      </c>
+      <c r="X40" s="8" t="n">
+        <v>21.7</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>81.3</v>
+        <v>85.5</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3902,40 +3779,40 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>48.8</v>
+        <v>1448.8</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>29.4</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F41" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F41" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>9.9</v>
+        <v>19.9</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>12.4</v>
+        <v>17.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.1</v>
+        <v>13</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="L41" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L41" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>10.8</v>
+        <v>20.8</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>89.09999999999999</v>
@@ -3946,32 +3823,32 @@
       <c r="Q41" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>58.4</v>
+        <v>584.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>28.5</v>
+        <v>4.6</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>25.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>0.1</v>
+        <v>174</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2.6</v>
+        <v>19.6</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3986,81 +3863,77 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">442
-2 6
-</t>
-        </is>
+      <c r="C42" s="3" t="n">
+        <v>464.3</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>33.1</v>
+        <v>32.8</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G42" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>924.9</v>
+      </c>
+      <c r="G42" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>4.4</v>
+        <v>14.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>5.8</v>
+        <v>20.1</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>12.2</v>
+        <v>2.8</v>
+      </c>
+      <c r="L42" s="8" t="n">
+        <v>72.8</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>16.1</v>
+        <v>16.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>12.6</v>
+        <v>17.6</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>89</v>
+        <v>289</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>2.1</v>
+        <v>12.1</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>24.7</v>
+        <v>30.8</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>25.4</v>
+        <v>22.6</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>22.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>5.2</v>
+        <v>130</v>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v>22.2</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>63.2</v>
+        <v>27.5</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>21.4</v>
+        <v>23.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>24.4</v>
+        <v>0.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>6.1</v>
+        <v>3.7</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4076,25 +3949,25 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>341.3</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>18.6</v>
+        <v>2341.3</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>88.59999999999999</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>15.3</v>
+        <v>25.3</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="H43" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>2.2</v>
+        <v>24.9</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>2.8</v>
@@ -4115,37 +3988,37 @@
         <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>66.3</v>
+        <v>12.5</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="R43" s="8" t="n">
+        <v>22.3</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>12.3</v>
+        <v>25.4</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>21.1</v>
+        <v>181.4</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>61.1</v>
+        <v>15.7</v>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>791.4</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>0.8</v>
+        <v>182.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>4.6</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4163,14 +4036,14 @@
       <c r="C44" s="3" t="n">
         <v>141.6</v>
       </c>
-      <c r="D44" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>19.8</v>
+      <c r="D44" s="8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>21.5</v>
+        <v>44.5</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>4.9</v>
@@ -4179,59 +4052,53 @@
         <v>18.6</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>82.8</v>
+        <v>10.8</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>19.7</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1</v>
+        <v>19.4</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>19.5</v>
+        <v>1.4</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>20.1</v>
+        <v>6.5</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>89</v>
+        <v>390.1</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>3.3</v>
+        <v>12.4</v>
+      </c>
+      <c r="Q44" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>2.2</v>
+        <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>22.9</v>
+        <v>22.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>7</v>
+        <v>181</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v>33.5</v>
+        <v>15.1</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>22.3</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>73.8</v>
-      </c>
+        <v>20.2</v>
+      </c>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4245,79 +4112,59 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>77.7</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="C45" s="3" t="n">
+        <v>16871.1</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
       <c r="I45" s="3" t="n">
-        <v>13.3</v>
+        <v>123.3</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>165.6</v>
+        <v>116.6</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>30</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>1825.6</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>67.7</v>
-      </c>
+        <v>110.4</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>37.2</v>
+        <v>10234.2</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2.4</v>
+        <v>1167.4</v>
       </c>
       <c r="Q45" s="3" t="n">
+        <v>1691.2</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="S45" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R45" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>22.9</v>
-      </c>
       <c r="T45" s="3" t="n">
-        <v>69</v>
+        <v>4084.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V45" s="3" t="n">
-        <v>242.4</v>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v>21.8</v>
-      </c>
+        <v>112.2</v>
+      </c>
+      <c r="V45" s="3" t="inlineStr"/>
+      <c r="W45" s="3" t="inlineStr"/>
       <c r="X45" s="3" t="n">
-        <v>124.2</v>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 7
-57
-</t>
-        </is>
+        <v>184832438.2</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>81.5</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>5.8</v>
+        <v>15.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4333,43 +4180,38 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D46" s="3" t="n">
+        <v>311.7</v>
+      </c>
+      <c r="D46" s="8" t="n">
         <v>29</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="3" t="n">
-        <v>1.1</v>
+      <c r="H46" s="8" t="n">
+        <v>67.59999999999999</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>825.6</v>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20 8
-</t>
-        </is>
+      <c r="M46" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>89</v>
@@ -4377,36 +4219,34 @@
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
+      <c r="Q46" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="R46" s="8" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>22.9</v>
+      </c>
       <c r="T46" s="3" t="n">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="V46" s="8" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 7
-57
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="W46" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,62 +736,64 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>9437.5</v>
+        <v>83.7</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>31.2</v>
+        <v>18.2</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.4</v>
+        <v>17.2</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>24.2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>14.4</v>
+        <v>14</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>91241.10000000001</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="L4" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>82.5</v>
+        <v>178.5</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="S4" s="8" t="n">
+      <c r="S4" s="3" t="n">
         <v>27</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>631.1</v>
+        <v>63.7</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>18.1</v>
+        <v>27.7</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24</v>
@@ -812,28 +814,28 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="8" t="n">
+      <c r="C5" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>21.5</v>
+        <v>13.5</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="8" t="n">
-        <v>87.40000000000001</v>
-      </c>
+      <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>25.8</v>
+        <v>9.6</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>19.1</v>
@@ -841,37 +843,41 @@
       <c r="M5" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="N5" s="8" t="n">
-        <v>19.9</v>
+      <c r="N5" s="3" t="n">
+        <v>89.90000000000001</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Q5" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>187.8</v>
+        <v>87.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>12.9</v>
+        <v>2.7</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="n">
-        <v>27.5</v>
+      <c r="W5" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="X5" s="8" t="n">
+        <v>72.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>726.1</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>9.699999999999999</v>
@@ -890,9 +896,9 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>432.4</v>
-      </c>
-      <c r="D6" s="8" t="n">
+        <v>831.6</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" s="3" t="n">
@@ -904,60 +910,62 @@
       <c r="G6" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="3" t="n">
         <v>19</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>188.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="Q6" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q6" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="8" t="n">
-        <v>232.9</v>
+      <c r="R6" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>651.1</v>
+        <v>25.9</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>1608.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="V6" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>185</v>
+        <v>85</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -973,71 +981,71 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1437.3</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>33</v>
+        <v>143.7</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>251.1</v>
-      </c>
-      <c r="G7" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
+        <v>14.8</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="J7" s="3" t="n">
-        <v>14.9</v>
+        <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>13.1</v>
+        <v>0</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>12.3</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="N7" s="8" t="n">
-        <v>67.3</v>
+      <c r="N7" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>187.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>31.9</v>
+        <v>21.9</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="S7" s="8" t="n">
+      <c r="S7" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>2022.1</v>
+        <v>52.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="3" t="n">
         <v>27.6</v>
       </c>
-      <c r="W7" s="8" t="n">
-        <v>24.1</v>
-      </c>
+      <c r="W7" s="3" t="inlineStr"/>
       <c r="X7" s="8" t="n">
-        <v>27.8</v>
+        <v>26.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>177.9</v>
+        <v>1772.9</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>17.5</v>
@@ -1056,15 +1064,15 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1297.2</v>
+        <v>98971.60000000001</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>32.6</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F8" s="8" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F8" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1074,40 +1082,40 @@
         <v>17.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>16.9</v>
+        <v>1.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K8" s="8" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="L8" s="8" t="n">
+      <c r="K8" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>20</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="N8" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>187.7</v>
+        <v>87.7</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="3" t="n">
         <v>33.2</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>2524.1</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>11.6</v>
@@ -1118,15 +1126,13 @@
       <c r="W8" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X8" s="8" t="n">
+      <c r="X8" s="3" t="n">
         <v>27</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>90.2</v>
       </c>
-      <c r="Z8" s="3" t="n">
-        <v>2.9</v>
-      </c>
+      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1141,64 +1147,74 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1666.5</v>
+        <v>166.6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>852.6</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+        <v>1152.6</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>122.9</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>681.1</v>
+        <v>8</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>80.5</v>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="n">
+        <v>211.2</v>
+      </c>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>44.3</v>
+        <v>44</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>194.3</v>
+        <v>94.3</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>187.8</v>
+        <v>87.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>196.3</v>
+        <v>96.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1440.9</v>
+        <v>1840.9</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>162.9</v>
+        <v>12.9</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1138.8</v>
+        <v>138.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1617.3</v>
+        <v>1217.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>132.9</v>
+        <v>1831.9</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>1360.9</v>
+        <v>360.9</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>1126.1</v>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
+        <v>126.1</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>113</v>
+      </c>
       <c r="X9" s="3" t="inlineStr"/>
-      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="n">
+        <v>11418.4</v>
+      </c>
       <c r="Z9" s="3" t="n">
-        <v>32.8</v>
+        <v>58.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1214,13 +1230,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>333.3</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>5.1</v>
+        <v>33.3</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>30.5</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>185.1</v>
+        <v>18.5</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>24.5</v>
@@ -1228,25 +1244,29 @@
       <c r="G10" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>16.1</v>
+      <c r="H10" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.2</v>
+        <v>15.2</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="8" t="n">
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="N10" s="8" t="n">
+        <v>19.3</v>
+      </c>
       <c r="O10" s="3" t="n">
-        <v>188.2</v>
+        <v>88.5</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>2.6</v>
@@ -1254,29 +1274,29 @@
       <c r="Q10" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="R10" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="S10" s="8" t="n">
+      <c r="S10" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>272.2</v>
+        <v>72.2</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>0.5</v>
+        <v>25.2</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X10" s="3" t="n">
+      <c r="X10" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>180.5</v>
+        <v>80.5</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>16.6</v>
@@ -1295,7 +1315,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1445</v>
+        <v>1445.1</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>28.7</v>
@@ -1303,7 +1323,7 @@
       <c r="E11" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1313,55 +1333,59 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>13.3</v>
+        <v>3.9</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
+        <v>80.59999999999999</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>20.7</v>
+        <v>46.7</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>187.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>41.9</v>
+        <v>27.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>981.9</v>
+        <v>230.8</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="V11" s="8" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V11" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="W11" s="8" t="n">
-        <v>24.7</v>
+      <c r="W11" s="3" t="n">
+        <v>4.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>30.9</v>
+        <v>31.9</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>197.5</v>
-      </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+        <v>97.5</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>10.8</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1376,34 +1400,34 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>383.6</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>28.1</v>
+        <v>318.3</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>98.09999999999999</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>18</v>
+        <v>8.5</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>81.09999999999999</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>19.3</v>
@@ -1415,10 +1439,10 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>27.8</v>
+        <v>2.7</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>27.2</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>25.2</v>
@@ -1427,25 +1451,25 @@
         <v>30.8</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>8544.1</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="V12" s="8" t="n">
+      <c r="V12" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="W12" s="8" t="n">
-        <v>284.4</v>
-      </c>
-      <c r="X12" s="8" t="n">
+      <c r="W12" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X12" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>197.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>10.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1461,9 +1485,9 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>39356.7</v>
-      </c>
-      <c r="D13" s="8" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="D13" s="3" t="n">
         <v>31.1</v>
       </c>
       <c r="E13" s="3" t="n">
@@ -1475,19 +1499,19 @@
       <c r="G13" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>12.6</v>
+        <v>0.1</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="L13" s="8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>20</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1497,10 +1521,12 @@
         <v>20.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>189.1</v>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="8" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q13" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1512,23 +1538,23 @@
       <c r="T13" s="3" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="U13" s="8" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="V13" s="8" t="n">
+      <c r="U13" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="V13" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="8" t="n">
+      <c r="W13" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="X13" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>197.7</v>
+        <v>192.9</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>10.7</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1544,7 +1570,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>13974</v>
+        <v>32.4</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>32.5</v>
@@ -1559,29 +1585,31 @@
         <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>1.3</v>
+      </c>
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="L14" s="8" t="n">
+      <c r="L14" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>189.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>30.6</v>
@@ -1590,7 +1618,7 @@
         <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>50.9</v>
@@ -1627,41 +1655,43 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>433.5</v>
+        <v>1643.3</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>29.5</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F15" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.9</v>
+        <v>11.9</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>10</v>
+        <v>0.8</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
+        <v>19.1</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>21.3</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>188.8</v>
+        <v>88.8</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>2.6</v>
@@ -1672,26 +1702,26 @@
       <c r="R15" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S15" s="8" t="n">
+      <c r="S15" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>163.8</v>
+        <v>63.8</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="V15" s="8" t="n">
+      <c r="V15" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="W15" s="8" t="n">
-        <v>241.1</v>
+      <c r="W15" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>174</v>
+        <v>1741</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>17.9</v>
@@ -1710,22 +1740,22 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>11992.8</v>
+        <v>199.2</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>149.9</v>
+        <v>1129.9</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>991.8</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>124.7</v>
+        <v>124.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>150.8</v>
+        <v>50.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>190.3</v>
+        <v>9</v>
       </c>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="n">
@@ -1735,42 +1765,46 @@
         <v>16</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1100.9</v>
+        <v>460.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>194.6</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>105.2</v>
+        <v>1055.9</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>444.1</v>
+        <v>4464.1</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>12.9</v>
+        <v>102.9</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1142.8</v>
+        <v>142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>123</v>
+        <v>1123</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>142.5</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>1368.7</v>
+        <v>368.7</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>533441.5</v>
+        <v>53.1</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="3" t="inlineStr"/>
-      <c r="X16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>137.5</v>
+      </c>
       <c r="Y16" s="3" t="n">
-        <v>1455.1</v>
+        <v>455.1</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>13.4</v>
@@ -1789,62 +1823,58 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>39.9</v>
+        <v>5.8</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F17" s="8" t="n">
-        <v>224.9</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="F17" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="I17" s="8" t="n">
-        <v>81.2</v>
+      <c r="I17" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="8" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="M17" s="8" t="n">
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="N17" s="8" t="n">
-        <v>20</v>
+      <c r="N17" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>188.8</v>
+        <v>88.8</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="8" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>946.4</v>
+      <c r="Q17" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="R17" s="8" t="n">
+        <v>82</v>
       </c>
       <c r="S17" s="8" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>173.7</v>
+        <v>23.7</v>
       </c>
       <c r="U17" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>24.2</v>
+        <v>48.2</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>23</v>
@@ -1872,56 +1902,56 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>437.5</v>
+        <v>0.1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="8" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="I18" s="8" t="n">
-        <v>39.5</v>
+        <v>40.8</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>844.1</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>18</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>19.2</v>
+        <v>9.6</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>12.7</v>
+        <v>27.7</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>19.3</v>
+        <v>1.9</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="Q18" s="8" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Q18" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S18" s="8" t="n">
+      <c r="S18" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>163.1</v>
+        <v>6.2</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>14.4</v>
@@ -1929,11 +1959,11 @@
       <c r="V18" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="X18" s="3" t="n">
-        <v>31</v>
+      <c r="X18" s="8" t="n">
+        <v>11.3</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>92.09999999999999</v>
@@ -1955,77 +1985,75 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1423.9</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>32.5</v>
+        <v>43.3</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>22.5</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="G19" s="8" t="n">
-        <v>124.8</v>
+      <c r="G19" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.1</v>
+        <v>11.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>13.5</v>
+        <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>28.5</v>
+        <v>91.5</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>20</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>2.3</v>
+        <v>87.5</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>31.8</v>
+        <v>2.8</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>61.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>25.3</v>
+        <v>94.2</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <v>295.3</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>62.1</v>
+        <v>54</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>25.8</v>
+        <v>655.8</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="3" t="n">
         <v>27</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>181.2</v>
-      </c>
-      <c r="Z19" s="3" t="n">
-        <v>16.2</v>
-      </c>
+        <v>81.8</v>
+      </c>
+      <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2040,39 +2068,37 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>256.8</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>27.2</v>
+        <v>856.8</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>88.40000000000001</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="8" t="n">
-        <v>23.5</v>
+      <c r="F20" s="3" t="n">
+        <v>25.5</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="H20" s="8" t="n">
-        <v>82.2</v>
+      <c r="H20" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>2408</v>
-      </c>
-      <c r="L20" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N20" s="8" t="n">
+      <c r="N20" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
@@ -2082,31 +2108,31 @@
         <v>12.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R20" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R20" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>70.7</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>19.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="8" t="n">
+      <c r="W20" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>167.2</v>
+        <v>67.2</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>10.2</v>
@@ -2125,9 +2151,9 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1433.5</v>
-      </c>
-      <c r="D21" s="8" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="D21" s="3" t="n">
         <v>30.8</v>
       </c>
       <c r="E21" s="3" t="n">
@@ -2140,29 +2166,33 @@
         <v>12.4</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>17.7</v>
+        <v>1.7</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>1.4</v>
+        <v>12.3</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>186.7</v>
-      </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="8" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="R21" s="3" t="n">
@@ -2172,16 +2202,16 @@
         <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="V21" s="8" t="n">
+      <c r="V21" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>2.2</v>
+        <v>22.4</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>25.9</v>
@@ -2206,28 +2236,26 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>374</v>
+        <v>34.4</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="3" t="n">
-        <v>17.2</v>
-      </c>
+      <c r="E22" s="3" t="inlineStr"/>
       <c r="F22" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" s="8" t="n">
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="I22" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I22" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3.7</v>
@@ -2242,10 +2270,10 @@
         <v>17.5</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>21.6</v>
+        <v>87</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>30.2</v>
@@ -2253,29 +2281,29 @@
       <c r="R22" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="S22" s="8" t="n">
+      <c r="S22" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>156.4</v>
+        <v>56.4</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="8" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>19.5</v>
+      <c r="V22" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W22" s="8" t="n">
+        <v>93.5</v>
       </c>
       <c r="X22" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>185.5</v>
+        <v>85.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2297,13 +2325,13 @@
         <v>153.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>92.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1123</v>
+        <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>160.3</v>
+        <v>16027.4</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>85.59999999999999</v>
@@ -2312,44 +2340,52 @@
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>135.5</v>
+        <v>15.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>49.9</v>
+        <v>49.5</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>195.2</v>
+        <v>95.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1882.8</v>
+        <v>88.2</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>196.5</v>
+        <v>96.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1437.2</v>
+        <v>1137.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
+        <v>1535.7</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>1145.1</v>
+      </c>
       <c r="S23" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>1295.2</v>
+        <v>295.2</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>85.2</v>
       </c>
-      <c r="V23" s="3" t="inlineStr"/>
-      <c r="W23" s="3" t="inlineStr"/>
+      <c r="V23" s="3" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>210.7</v>
+      </c>
       <c r="X23" s="3" t="n">
-        <v>1126.7</v>
+        <v>226.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>1411</v>
+        <v>1811</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>27.1</v>
@@ -2368,44 +2404,48 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>385.1</v>
+        <v>88.5</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>30.6</v>
+        <v>20.6</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="8" t="n">
-        <v>24.6</v>
+      <c r="F24" s="3" t="n">
+        <v>84.59999999999999</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>87.40000000000001</v>
+        <v>12.9</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>5.1</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="N24" s="8" t="n">
-        <v>19.5</v>
+      <c r="N24" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>187.4</v>
-      </c>
-      <c r="P24" s="3" t="inlineStr"/>
-      <c r="Q24" s="8" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Q24" s="3" t="n">
         <v>29.2</v>
       </c>
       <c r="R24" s="3" t="n">
@@ -2415,23 +2455,21 @@
         <v>23.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="V24" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="V24" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="X24" s="8" t="n">
+      <c r="X24" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="Y24" s="3" t="n">
-        <v>182.2</v>
-      </c>
+      <c r="Y24" s="3" t="inlineStr"/>
       <c r="Z24" s="3" t="n">
         <v>5.4</v>
       </c>
@@ -2449,74 +2487,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1374</v>
+        <v>374</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>32.1</v>
+        <v>42.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>25.7</v>
+        <v>19.9</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>9.1</v>
+        <v>12.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>81414.60000000001</v>
+      </c>
       <c r="L25" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="N25" s="8" t="n">
+      <c r="N25" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q25" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Q25" s="3" t="n">
         <v>31.3</v>
       </c>
-      <c r="R25" s="3" t="n">
-        <v>243.1</v>
-      </c>
-      <c r="S25" s="8" t="n">
+      <c r="R25" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S25" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>956.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>224.2</v>
-      </c>
-      <c r="W25" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="W25" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="X25" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>1747.6</v>
+        <v>174.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>7.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2532,7 +2572,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>329.8</v>
+        <v>329.2</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>30.8</v>
@@ -2546,32 +2586,32 @@
       <c r="G26" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="H26" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="I26" s="8" t="n">
-        <v>11.9</v>
+      <c r="H26" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N26" s="8" t="n">
-        <v>949.2</v>
+        <v>17.6</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>24.4</v>
@@ -2583,23 +2623,21 @@
         <v>24.5</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="V26" s="8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V26" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="X26" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X26" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="Y26" s="3" t="n">
-        <v>181.1</v>
-      </c>
+      <c r="Y26" s="3" t="inlineStr"/>
       <c r="Z26" s="3" t="n">
         <v>17.6</v>
       </c>
@@ -2617,16 +2655,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.8</v>
+        <v>952.2</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="E27" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>23.8</v>
+      <c r="E27" s="8" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>18.8</v>
@@ -2634,50 +2672,52 @@
       <c r="H27" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="8" t="n">
-        <v>21.9</v>
+      <c r="I27" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="L27" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="N27" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>187.5</v>
+        <v>82.5</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="Q27" s="8" t="n">
-        <v>6</v>
+        <v>2.9</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>26</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>21.6</v>
+        <v>22.6</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>168.4</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v>23.2</v>
+        <v>68.40000000000001</v>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="W27" s="8" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X27" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="X27" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y27" s="3" t="n">
@@ -2700,13 +2740,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>9389.299999999999</v>
+        <v>288.9</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>20.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>25</v>
@@ -2714,17 +2754,17 @@
       <c r="G28" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K28" s="3" t="n">
         <v>19</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J28" s="8" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>19.6</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>20.6</v>
@@ -2733,40 +2773,40 @@
         <v>19.2</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>21.3</v>
+        <v>281.3</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>187.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>2.9</v>
+        <v>11.4</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="3" t="n">
         <v>23</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>164.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="V28" s="8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="V28" s="3" t="n">
         <v>26</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>23.6</v>
+        <v>55.6</v>
       </c>
       <c r="X28" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>16</v>
@@ -2785,16 +2825,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>408.5</v>
+        <v>140.8</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>29.4</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>20.3</v>
+        <v>503.1</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>24.9</v>
+        <v>22.9</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>19.1</v>
@@ -2803,7 +2843,7 @@
         <v>20.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>16.7</v>
+        <v>11.7</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2.9</v>
@@ -2817,23 +2857,23 @@
       <c r="M29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="8" t="n">
+      <c r="N29" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="Q29" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q29" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="8" t="n">
-        <v>226.5</v>
+      <c r="S29" s="3" t="n">
+        <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>162.6</v>
@@ -2841,17 +2881,17 @@
       <c r="U29" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="V29" s="8" t="n">
+      <c r="V29" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="X29" s="3" t="n">
+      <c r="X29" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>8182.8</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>16.1</v>
@@ -2870,22 +2910,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1856.4</v>
+        <v>11836.4</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>150.3</v>
+        <v>150.5</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>97.8</v>
+        <v>0.8</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>124.1</v>
+        <v>1224.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>152.5</v>
+        <v>52.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>191.9</v>
+        <v>9.1</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>180</v>
@@ -2894,49 +2934,49 @@
         <v>15.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>125.4</v>
+        <v>25.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>199.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1103.2</v>
+        <v>9103.4</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>1441.9</v>
+        <v>14241.9</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>13.1</v>
+        <v>10.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1138.5</v>
+        <v>138.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1113.7</v>
+        <v>113.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>122.8</v>
+        <v>122.7</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>1332.8</v>
+        <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>164.5</v>
+        <v>16.4</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1823.1</v>
+        <v>1123.1</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>1124.3</v>
+        <v>164.3</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>1399.8</v>
+        <v>39.4</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>32.6</v>
@@ -2955,22 +2995,22 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>383.1</v>
+        <v>11.4</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>30.1</v>
+        <v>20.1</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>24.8</v>
+        <v>94.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>184.5</v>
+        <v>10.5</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>182.4</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2</v>
@@ -2978,52 +3018,52 @@
       <c r="J31" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n">
+      <c r="K31" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L31" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>6.4</v>
+        <v>20.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>188.4</v>
+        <v>22.4</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="Q31" s="8" t="n">
+      <c r="Q31" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="S31" s="8" t="n">
-        <v>24.5</v>
+      <c r="S31" s="3" t="n">
+        <v>845.8</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>166.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="V31" s="8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V31" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="W31" s="8" t="n">
+      <c r="W31" s="3" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z31" s="3" t="n">
-        <v>6.5</v>
-      </c>
+        <v>80.90000000000001</v>
+      </c>
+      <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3038,72 +3078,76 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>437.3</v>
+        <v>943.7</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E32" s="8" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="E32" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>865.1</v>
-      </c>
-      <c r="G32" s="3" t="inlineStr"/>
+        <v>26.9</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="H32" s="3" t="n">
-        <v>18.5</v>
+        <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>13.5</v>
+        <v>3.9</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="N32" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N32" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>188.4</v>
-      </c>
-      <c r="P32" s="3" t="inlineStr"/>
+        <v>88.40000000000001</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="Q32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>156.6</v>
+        <v>560.6</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v>23.7</v>
+        <v>1.9</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>128.8</v>
       </c>
       <c r="X32" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>169.1</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>1118.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3119,38 +3163,40 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1397</v>
+        <v>397.1</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E33" s="8" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="E33" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>26.7</v>
+      <c r="F33" s="8" t="n">
+        <v>65.7</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>34.1</v>
+        <v>13.9</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>17.9</v>
+        <v>12.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr"/>
-      <c r="K33" s="3" t="n">
-        <v>10</v>
+        <v>11.4</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>1.1</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>49.5</v>
+        <v>19.5</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>26.7</v>
+        <v>21.7</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>87.40000000000001</v>
@@ -3158,32 +3204,32 @@
       <c r="P33" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q33" s="8" t="n">
+      <c r="Q33" s="3" t="n">
         <v>32.9</v>
       </c>
       <c r="R33" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="S33" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="S33" s="3" t="n">
-        <v>63.4</v>
-      </c>
       <c r="T33" s="3" t="n">
-        <v>1947.7</v>
-      </c>
-      <c r="U33" s="8" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="V33" s="8" t="n">
+      <c r="V33" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>127.6</v>
+        <v>122.6</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>17.4</v>
@@ -3202,10 +3248,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>362.4</v>
+        <v>36.2</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>30.4</v>
+        <v>10.4</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>20.2</v>
@@ -3213,20 +3259,20 @@
       <c r="F34" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K34" s="3" t="n">
-        <v>4.2</v>
+      <c r="K34" s="8" t="n">
+        <v>2.4</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>20.4</v>
@@ -3238,26 +3284,28 @@
         <v>21</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>187.3</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr"/>
+        <v>87.3</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="Q34" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S34" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="S34" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>7886.8</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>17.2</v>
+        <v>7.5</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>55.4</v>
+        <v>25.5</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>23.3</v>
@@ -3266,10 +3314,10 @@
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>183.2</v>
+        <v>1832.8</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3287,74 +3335,74 @@
       <c r="C35" s="3" t="n">
         <v>187.9</v>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>23.9</v>
+        <v>3.9</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18.7</v>
+        <v>1.8</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L35" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N35" s="8" t="n">
-        <v>9.300000000000001</v>
+      <c r="N35" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>854.1</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Q35" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q35" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S35" s="8" t="n">
+      <c r="S35" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>88.5</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V35" s="8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="V35" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="X35" s="8" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X35" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>188.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>2.9</v>
+        <v>12.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3372,11 +3420,11 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="8" t="n">
-        <v>20</v>
+      <c r="E36" s="3" t="n">
+        <v>100.1</v>
       </c>
       <c r="F36" s="8" t="n">
         <v>24.3</v>
@@ -3391,10 +3439,10 @@
         <v>2.2</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>20.6</v>
@@ -3402,45 +3450,43 @@
       <c r="M36" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="N36" s="8" t="n">
+      <c r="N36" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="8" t="n">
+      <c r="Q36" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="R36" s="8" t="n">
+      <c r="R36" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S36" s="8" t="n">
-        <v>593.8</v>
+      <c r="S36" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>72.3</v>
+        <v>822.5</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="V36" s="8" t="n">
-        <v>5</v>
+        <v>95.8</v>
       </c>
       <c r="W36" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>24.8</v>
+        <v>46.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>178.2</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>16.9</v>
-      </c>
+        <v>78.2</v>
+      </c>
+      <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3457,14 +3503,20 @@
       <c r="C37" s="3" t="n">
         <v>11683.5</v>
       </c>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="n">
+        <v>1450.1</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>125.5</v>
+      </c>
       <c r="G37" s="3" t="n">
         <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>192.4</v>
+        <v>9224.1</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>12.6</v>
@@ -3473,44 +3525,52 @@
         <v>15.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>160.8</v>
+        <v>10.2</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="n">
+        <v>1396.5</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>127.2</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>1432.5</v>
+        <v>437.5</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>139.6</v>
+        <v>129</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>126.8</v>
+        <v>126</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>3431.1</v>
+        <v>343.7</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>165.7</v>
+        <v>65.7</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="3" t="inlineStr"/>
-      <c r="X37" s="3" t="inlineStr"/>
+      <c r="W37" s="3" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>127.1</v>
+      </c>
       <c r="Y37" s="3" t="n">
         <v>396.6</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>342.4</v>
+        <v>34.4</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3535,21 +3595,23 @@
         <v>20.2</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.4</v>
+        <v>25.1</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>18.5</v>
+        <v>88.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J38" s="8" t="n">
-        <v>211.1</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
@@ -3557,13 +3619,13 @@
         <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>21.4</v>
+        <v>28.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>187.5</v>
+        <v>87.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>27.9</v>
@@ -3571,29 +3633,29 @@
       <c r="R38" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S38" s="8" t="n">
-        <v>25.2</v>
+      <c r="S38" s="3" t="n">
+        <v>23.2</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>168.7</v>
+        <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>18.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>22.4</v>
+        <v>224.2</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>79.3</v>
+        <v>179.3</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>18.9</v>
+        <v>16.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3609,76 +3671,74 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1400.8</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E39" s="8" t="n">
+        <v>14001.8</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E39" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>12.3</v>
+      <c r="G39" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="I39" s="3" t="n">
-        <v>52.5</v>
-      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
-        <v>3.9</v>
+        <v>29.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>20.5</v>
+        <v>0</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>10.5</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="8" t="n">
-        <v>22</v>
+      <c r="N39" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="P39" s="8" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="Q39" s="8" t="n">
+      <c r="P39" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>23.1</v>
+        <v>25.1</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>345.1</v>
+        <v>534.5</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" s="8" t="n">
+      <c r="V39" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="W39" s="8" t="n">
+      <c r="W39" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X39" s="8" t="n">
-        <v>27.6</v>
+      <c r="X39" s="3" t="n">
+        <v>97.59999999999999</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>175.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>17.6</v>
+        <v>13.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3697,28 +3757,28 @@
         <v>74.40000000000001</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>20.2</v>
+        <v>444.6</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>90.2</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H40" s="8" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>14.9</v>
+        <v>4.9</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>20.4</v>
@@ -3726,16 +3786,16 @@
       <c r="M40" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="N40" s="8" t="n">
-        <v>10.1</v>
+      <c r="N40" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>88</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Q40" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q40" s="3" t="n">
         <v>21</v>
       </c>
       <c r="R40" s="3" t="n">
@@ -3745,25 +3805,25 @@
         <v>22.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>189.7</v>
+        <v>89.7</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>19.6</v>
+        <v>28.3</v>
+      </c>
+      <c r="W40" s="8" t="n">
+        <v>90.59999999999999</v>
       </c>
       <c r="X40" s="8" t="n">
-        <v>21.7</v>
+        <v>217.2</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>85.5</v>
+        <v>181.5</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>5.7</v>
+        <v>19.9</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3779,10 +3839,10 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1448.8</v>
+        <v>114.8</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>29.4</v>
+        <v>494.3</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>19.5</v>
@@ -3793,19 +3853,19 @@
       <c r="G41" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="H41" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L41" s="8" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="K41" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L41" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="M41" s="3" t="n">
@@ -3823,26 +3883,26 @@
       <c r="Q41" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="8" t="n">
+      <c r="R41" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>584.5</v>
+        <v>58.4</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>4.6</v>
+        <v>24.6</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="X41" s="8" t="n">
-        <v>25.2</v>
+        <v>25.8</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>174</v>
@@ -3864,43 +3924,43 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>464.3</v>
+        <v>86.2</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>32.8</v>
+        <v>98.8</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F42" s="8" t="n">
-        <v>924.9</v>
-      </c>
-      <c r="G42" s="8" t="n">
+      <c r="F42" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G42" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>20.1</v>
+        <v>0.8</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L42" s="8" t="n">
-        <v>72.8</v>
+        <v>0.2</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>16.8</v>
+        <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>289</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>12.1</v>
@@ -3911,29 +3971,29 @@
       <c r="R42" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="S42" s="8" t="n">
+      <c r="S42" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="U42" s="8" t="n">
-        <v>22.2</v>
+        <v>28.2</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>0.2</v>
+        <v>25.8</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>10.4</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>87</v>
+        <v>18708</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>3.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3949,13 +4009,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2341.3</v>
-      </c>
-      <c r="D43" s="8" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="D43" s="3" t="n">
         <v>32</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>88.59999999999999</v>
+        <v>18.6</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>25.3</v>
@@ -3963,14 +4023,14 @@
       <c r="G43" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>24.9</v>
+        <v>2.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>15.2</v>
@@ -3988,37 +4048,35 @@
         <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q43" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="8" t="n">
+      <c r="R43" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>181.4</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="V43" s="8" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="W43" s="8" t="n">
-        <v>791.4</v>
+      <c r="W43" s="3" t="n">
+        <v>22.4</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="Y43" s="3" t="n">
         <v>182.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4034,16 +4092,16 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>141.6</v>
-      </c>
-      <c r="D44" s="8" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="D44" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="E44" s="8" t="n">
+      <c r="E44" s="3" t="n">
         <v>19</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>44.5</v>
+        <v>21.5</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>4.9</v>
@@ -4051,8 +4109,8 @@
       <c r="H44" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I44" s="3" t="n">
-        <v>10.8</v>
+      <c r="I44" s="8" t="n">
+        <v>80.8</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>0.6</v>
@@ -4064,34 +4122,34 @@
         <v>19.4</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>6.5</v>
+        <v>19.9</v>
+      </c>
+      <c r="N44" s="8" t="n">
+        <v>0.8</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>390.1</v>
+        <v>189</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="Q44" s="8" t="n">
-        <v>28.6</v>
+      <c r="Q44" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>181</v>
+        <v>181.9</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>22.3</v>
+        <v>15.9</v>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v>822.3</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>20.2</v>
@@ -4113,52 +4171,66 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>16871.1</v>
-      </c>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr"/>
+        <v>18841.1</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>841.1</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>160.2</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>105.6</v>
+      </c>
       <c r="I45" s="3" t="n">
-        <v>123.3</v>
+        <v>169</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>116.6</v>
+        <v>16.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>30</v>
+        <v>2816.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>110.4</v>
+        <v>12180.4</v>
       </c>
       <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="n">
+        <v>110109210619.1</v>
+      </c>
       <c r="O45" s="3" t="n">
-        <v>10234.2</v>
+        <v>204.1</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1167.4</v>
+        <v>16808.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1691.2</v>
+        <v>1257.2</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>129.7</v>
+        <v>1291.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>26.2</v>
+        <v>18317.9</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>4084.4</v>
+        <v>44841.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>112.2</v>
+        <v>81.5</v>
       </c>
       <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
+      <c r="W45" s="3" t="n">
+        <v>1122.2</v>
+      </c>
       <c r="X45" s="3" t="n">
-        <v>184832438.2</v>
+        <v>924.7</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>81.5</v>
@@ -4180,30 +4252,32 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>311.7</v>
-      </c>
-      <c r="D46" s="8" t="n">
+        <v>511.7</v>
+      </c>
+      <c r="D46" s="3" t="n">
         <v>29</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>10.1</v>
+      <c r="G46" s="8" t="n">
+        <v>20.1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>2.2</v>
+        <v>17.6</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>122.6</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
       </c>
@@ -4211,7 +4285,7 @@
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>20.2</v>
+        <v>60.5</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>89</v>
@@ -4219,33 +4293,31 @@
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="R46" s="8" t="n">
+      <c r="Q46" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R46" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="8" t="n">
+      <c r="V46" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="W46" s="8" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>81.5</v>
-      </c>
+        <v>18.8</v>
+      </c>
+      <c r="X46" s="8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
@@ -738,20 +738,20 @@
       <c r="C4" s="3" t="n">
         <v>83.7</v>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>18.2</v>
+      <c r="D4" s="3" t="n">
+        <v>31.2</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>91241.10000000001</v>
+        <v>91124.10000000001</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.1</v>
@@ -760,16 +760,16 @@
         <v>4.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>17.6</v>
+        <v>88.8</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>75.59999999999999</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>178.5</v>
+      <c r="N4" s="3" t="n">
+        <v>17.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
@@ -793,7 +793,7 @@
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>27.7</v>
+        <v>27.2</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24</v>
@@ -823,20 +823,18 @@
       <c r="E5" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="F5" s="8" t="n">
-        <v>13.5</v>
+      <c r="F5" s="3" t="n">
+        <v>21.5</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="n">
         <v>19.1</v>
       </c>
@@ -844,14 +842,12 @@
         <v>18</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="P5" s="3" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
         <v>20.5</v>
       </c>
@@ -865,19 +861,19 @@
         <v>87.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="X5" s="8" t="n">
-        <v>72.5</v>
+      <c r="X5" s="3" t="n">
+        <v>27.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>726.1</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>9.699999999999999</v>
@@ -896,7 +892,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>831.6</v>
+        <v>432.6</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>31.4</v>
@@ -910,17 +906,17 @@
       <c r="G6" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20.3</v>
@@ -947,10 +943,10 @@
         <v>25.9</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1.6</v>
+        <v>18.6</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>26.2</v>
@@ -981,25 +977,25 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>143.7</v>
+        <v>43.7</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>23.8</v>
+        <v>33</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>25</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>14.8</v>
+        <v>84.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>18.2</v>
+        <v>2.2</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>4.9</v>
@@ -1007,17 +1003,17 @@
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="8" t="n">
+      <c r="L7" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="M7" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>17.3</v>
+      <c r="M7" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>27.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
@@ -1045,7 +1041,7 @@
         <v>26.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>1772.9</v>
+        <v>727.9</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>17.5</v>
@@ -1064,13 +1060,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>98971.60000000001</v>
+        <v>297.6</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>32.6</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>17.2</v>
+        <v>19.8</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>26.2</v>
@@ -1094,7 +1090,7 @@
         <v>20</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>20.5</v>
@@ -1150,10 +1146,10 @@
         <v>166.6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1152.6</v>
+        <v>152.6</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>122.9</v>
@@ -1165,7 +1161,7 @@
         <v>80.5</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>211.2</v>
+        <v>22.2</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
@@ -1183,7 +1179,7 @@
         <v>96.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1840.9</v>
+        <v>440.9</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>12.9</v>
@@ -1192,10 +1188,10 @@
         <v>138.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1217.3</v>
+        <v>117.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1831.9</v>
+        <v>1231.9</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>360.9</v>
@@ -1209,12 +1205,14 @@
       <c r="W9" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="X9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="Y9" s="3" t="n">
-        <v>11418.4</v>
+        <v>114102.4</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>58.8</v>
+        <v>38.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1245,17 +1243,13 @@
         <v>12</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>15.2</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>6.2</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
         <v>18.9</v>
       </c>
@@ -1266,7 +1260,7 @@
         <v>19.3</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>88.5</v>
+        <v>88.2</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>2.6</v>
@@ -1292,14 +1286,14 @@
       <c r="W10" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X10" s="8" t="n">
+      <c r="X10" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>80.5</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1315,7 +1309,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1445.1</v>
+        <v>2445.1</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>28.7</v>
@@ -1329,17 +1323,17 @@
       <c r="G11" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>18.2</v>
+      <c r="H11" s="8" t="n">
+        <v>85.2</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>20.1</v>
@@ -1347,35 +1341,35 @@
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="N11" s="8" t="n">
-        <v>46.7</v>
+      <c r="N11" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>230.8</v>
+        <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>5.7</v>
+        <v>58.7</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>25</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>4.1</v>
+        <v>2471.6</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>31.9</v>
@@ -1384,7 +1378,7 @@
         <v>97.5</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1400,10 +1394,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>318.3</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>98.09999999999999</v>
+        <v>383.3</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>28.1</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>19.6</v>
@@ -1414,8 +1408,8 @@
       <c r="G12" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="H12" s="8" t="n">
-        <v>81.09999999999999</v>
+      <c r="H12" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>2.9</v>
@@ -1424,7 +1418,7 @@
         <v>3.2</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>20.6</v>
@@ -1466,10 +1460,10 @@
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>197.7</v>
+        <v>97.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>19.7</v>
+        <v>0.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1485,7 +1479,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>35.6</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>31.1</v>
@@ -1493,8 +1487,8 @@
       <c r="E13" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>25.5</v>
+      <c r="F13" s="8" t="n">
+        <v>35.5</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>11.3</v>
@@ -1506,10 +1500,10 @@
         <v>1.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>5.3</v>
+        <v>0.3</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>20</v>
@@ -1547,11 +1541,11 @@
       <c r="W13" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X13" s="8" t="n">
+      <c r="X13" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>192.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.2</v>
@@ -1572,7 +1566,7 @@
       <c r="C14" s="3" t="n">
         <v>32.4</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="3" t="n">
         <v>32.5</v>
       </c>
       <c r="E14" s="3" t="n">
@@ -1585,14 +1579,12 @@
         <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
@@ -1600,7 +1592,7 @@
         <v>19.8</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>18.7</v>
+        <v>28.7</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>20.8</v>
@@ -1609,7 +1601,7 @@
         <v>89.90000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>30.6</v>
@@ -1618,7 +1610,7 @@
         <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>50.9</v>
@@ -1632,11 +1624,11 @@
       <c r="W14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>193</v>
+        <v>93</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>1.8</v>
@@ -1655,31 +1647,31 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1643.3</v>
+        <v>43.3</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="8" t="n">
-        <v>2.8</v>
+      <c r="E15" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>19.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>19.8</v>
+        <v>89.8</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.8</v>
+        <v>16.8</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>20.4</v>
@@ -1709,7 +1701,7 @@
         <v>63.8</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>14.1</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>24.5</v>
@@ -1721,7 +1713,7 @@
         <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>1741</v>
+        <v>74</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>17.9</v>
@@ -1743,13 +1735,13 @@
         <v>199.2</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1129.9</v>
+        <v>19249.9</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>991.8</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>124.2</v>
+        <v>124.7</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>50.8</v>
@@ -1757,7 +1749,9 @@
       <c r="H16" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="n">
+        <v>8.1</v>
+      </c>
       <c r="J16" s="3" t="n">
         <v>15.8</v>
       </c>
@@ -1765,25 +1759,25 @@
         <v>16</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>460.9</v>
+        <v>11.2</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>194.6</v>
+        <v>924.6</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1055.9</v>
+        <v>105.8</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4464.1</v>
+        <v>444.8</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>102.9</v>
+        <v>12.9</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1123</v>
+        <v>23</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>142.5</v>
@@ -1823,10 +1817,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>5.8</v>
+        <v>39.8</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>19.8</v>
@@ -1834,18 +1828,22 @@
       <c r="F17" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="H17" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>18.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="M17" s="3" t="n">
         <v>18.9</v>
       </c>
@@ -1853,7 +1851,7 @@
         <v>21</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>88.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>2.6</v>
@@ -1862,31 +1860,31 @@
         <v>28.6</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>82</v>
+        <v>8224</v>
       </c>
       <c r="S17" s="8" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="U17" s="8" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V17" s="8" t="n">
-        <v>48.2</v>
+      <c r="V17" s="3" t="n">
+        <v>24.2</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="X17" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>12.7</v>
+        <v>2.7</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1902,32 +1900,34 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>40.8</v>
       </c>
-      <c r="E18" s="8" t="n">
-        <v>91</v>
+      <c r="E18" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>844.1</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr"/>
+        <v>14.9</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="I18" s="3" t="n">
-        <v>1.5</v>
+        <v>24.9</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>9.6</v>
+        <v>19.6</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>27.7</v>
@@ -1936,10 +1936,10 @@
         <v>1.9</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>87.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>28.6</v>
@@ -1951,19 +1951,19 @@
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V18" s="8" t="n">
+      <c r="V18" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="X18" s="8" t="n">
-        <v>11.3</v>
+      <c r="W18" s="8" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>41</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>92.09999999999999</v>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>22.5</v>
+        <v>433.6</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>32.5</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>18.4</v>
@@ -1997,7 +1997,7 @@
         <v>25.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>11.6</v>
@@ -2006,7 +2006,7 @@
         <v>2.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>91.5</v>
@@ -2026,14 +2026,14 @@
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="8" t="n">
-        <v>61.8</v>
+      <c r="Q19" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="S19" s="8" t="n">
-        <v>295.3</v>
+        <v>24.2</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>54</v>
@@ -2041,8 +2041,8 @@
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="8" t="n">
-        <v>655.8</v>
+      <c r="V19" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>23.3</v>
@@ -2051,7 +2051,7 @@
         <v>27</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>81.8</v>
+        <v>81.2</v>
       </c>
       <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
@@ -2068,30 +2068,30 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>856.8</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>88.40000000000001</v>
+        <v>956.8</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>27.2</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>18.5</v>
+        <v>1.8</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J20" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="n">
+        <v>24.3</v>
+      </c>
       <c r="L20" s="3" t="n">
         <v>20</v>
       </c>
@@ -2102,22 +2102,22 @@
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>189</v>
+        <v>289</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>70.7</v>
+        <v>707.2</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>95.09999999999999</v>
@@ -2126,7 +2126,7 @@
         <v>24.9</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>20.5</v>
+        <v>106.1</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>21.2</v>
@@ -2175,7 +2175,7 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
@@ -2204,8 +2204,8 @@
       <c r="T21" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="U21" s="3" t="n">
-        <v>20.9</v>
+      <c r="U21" s="8" t="n">
+        <v>8.9</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.3</v>
@@ -2217,7 +2217,7 @@
         <v>25.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>185</v>
+        <v>850.8</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>14.5</v>
@@ -2236,23 +2236,25 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>34.4</v>
+        <v>374.1</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="F22" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>14.6</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I22" s="8" t="n">
-        <v>21.1</v>
+      <c r="I22" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.5</v>
@@ -2291,19 +2293,19 @@
         <v>18.7</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W22" s="8" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="X22" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="X22" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>85.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2322,16 +2324,16 @@
         <v>1925.5</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>153.1</v>
+        <v>155.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>16027.4</v>
+        <v>605.9</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>85.59999999999999</v>
@@ -2343,7 +2345,7 @@
         <v>15.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>49.5</v>
+        <v>495.3</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>95.2</v>
@@ -2355,16 +2357,16 @@
         <v>96.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1137.2</v>
+        <v>437.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1535.7</v>
+        <v>113.7</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>146.2</v>
+        <v>14.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1145.1</v>
+        <v>1143.1</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>19</v>
@@ -2376,16 +2378,16 @@
         <v>85.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>122.2</v>
+        <v>22.2</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>210.7</v>
+        <v>21</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>226.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>1811</v>
+        <v>1411</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>27.1</v>
@@ -2404,28 +2406,28 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>88.5</v>
+        <v>28.5</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="E24" s="3" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E24" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>11.2</v>
+        <v>1.7</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>0.1</v>
@@ -2437,16 +2439,16 @@
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>29.3</v>
+        <v>19.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>21.7</v>
+        <v>2.7</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>29.2</v>
+        <v>2.9</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>22.9</v>
@@ -2490,19 +2492,19 @@
         <v>374</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>42.1</v>
+        <v>12.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>19.9</v>
+        <v>19.3</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>20.7</v>
+        <v>25.7</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2.4</v>
@@ -2511,7 +2513,7 @@
         <v>3.6</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>81414.60000000001</v>
+        <v>1.6</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>19.5</v>
@@ -2523,40 +2525,40 @@
         <v>20.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>18.2</v>
+        <v>12.2</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>4</v>
+        <v>31.5</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>24</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>56.9</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V25" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>174.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2592,8 +2594,8 @@
       <c r="I26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>12.6</v>
+      <c r="J26" s="8" t="n">
+        <v>25.6</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.3</v>
@@ -2605,7 +2607,7 @@
         <v>17.6</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>19.2</v>
+        <v>89.2</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>87</v>
@@ -2620,13 +2622,13 @@
         <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>80</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>24.2</v>
@@ -2655,25 +2657,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>952.2</v>
+        <v>354.8</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>92.40000000000001</v>
+        <v>2.4</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>25.8</v>
+        <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>11.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>2.9</v>
@@ -2691,7 +2693,7 @@
         <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>82.5</v>
+        <v>87.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>2.9</v>
@@ -2700,7 +2702,7 @@
         <v>26</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>22.6</v>
+        <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23</v>
@@ -2708,20 +2710,20 @@
       <c r="T27" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U27" s="8" t="n">
-        <v>0.6</v>
+      <c r="U27" s="3" t="n">
+        <v>10.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W27" s="8" t="n">
-        <v>9.800000000000001</v>
+        <v>63.4</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>180.8</v>
+        <v>84.8</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>5.4</v>
@@ -2740,25 +2742,25 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>288.9</v>
+        <v>0.8</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>20.2</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>25</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.8</v>
@@ -2772,14 +2774,14 @@
       <c r="M28" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N28" s="8" t="n">
-        <v>281.3</v>
+      <c r="N28" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>11.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>28.2</v>
@@ -2794,19 +2796,19 @@
         <v>64.90000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>26</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="X28" s="8" t="n">
+        <v>956.1</v>
+      </c>
+      <c r="X28" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>16</v>
@@ -2825,19 +2827,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>140.8</v>
+        <v>20.8</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>29.4</v>
+        <v>49.4</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>503.1</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>22.9</v>
+        <v>613.1</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>20.1</v>
@@ -2858,13 +2860,13 @@
         <v>19.2</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>28.6</v>
@@ -2872,11 +2874,11 @@
       <c r="R29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="3" t="n">
+      <c r="S29" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>162.6</v>
+        <v>62.4</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>14.6</v>
@@ -2887,14 +2889,14 @@
       <c r="W29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="X29" s="8" t="n">
+      <c r="X29" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>8182.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>16.1</v>
+        <v>6.1</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2910,16 +2912,16 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11836.4</v>
+        <v>11856.4</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>150.5</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.8</v>
+        <v>97.8</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1224.1</v>
+        <v>124.1</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>52.5</v>
@@ -2928,7 +2930,7 @@
         <v>9.1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>15.8</v>
@@ -2937,22 +2939,22 @@
         <v>25.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>929.6</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>9103.4</v>
+        <v>103.4</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>14241.9</v>
+        <v>441.9</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>10.1</v>
+        <v>13.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>138.5</v>
+        <v>238.5</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>113.7</v>
@@ -2964,19 +2966,19 @@
         <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>16.4</v>
+        <v>6.4</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1123.1</v>
+        <v>123.1</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>164.3</v>
+        <v>61.3</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>39.4</v>
+        <v>43.9</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>32.6</v>
@@ -2995,13 +2997,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>11.4</v>
+        <v>33.4</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>20.1</v>
+        <v>30.8</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>94.8</v>
@@ -3010,7 +3012,7 @@
         <v>10.5</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>182.4</v>
+        <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2</v>
@@ -3018,10 +3020,8 @@
       <c r="J31" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L31" s="8" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="M31" s="3" t="n">
@@ -3031,10 +3031,10 @@
         <v>20.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>22.4</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>27.7</v>
@@ -3043,25 +3043,25 @@
         <v>22.7</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>845.8</v>
+        <v>24.5</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>66.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>24.6</v>
+        <v>1.2</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>824.6</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
@@ -3078,16 +3078,16 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>943.7</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>42.8</v>
+        <v>143.7</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>26.9</v>
+        <v>28.9</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>12.6</v>
@@ -3096,13 +3096,13 @@
         <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>20.6</v>
@@ -3111,13 +3111,13 @@
         <v>19.3</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>31</v>
@@ -3129,25 +3129,25 @@
         <v>25.4</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>560.6</v>
+        <v>56.6</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="V32" s="8" t="n">
-        <v>68.2</v>
+      <c r="V32" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="W32" s="8" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="X32" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X32" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>169.1</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>11.8</v>
+        <v>111.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3163,31 +3163,31 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>397.1</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>88.2</v>
+        <v>310.1</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>14.1</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F33" s="8" t="n">
-        <v>65.7</v>
+      <c r="F33" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>12.9</v>
+        <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>11.4</v>
+        <v>4.4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K33" s="8" t="n">
-        <v>1.1</v>
+      <c r="K33" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.9</v>
@@ -3207,8 +3207,8 @@
       <c r="Q33" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="R33" s="3" t="n">
-        <v>29.9</v>
+      <c r="R33" s="8" t="n">
+        <v>38.9</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>23.9</v>
@@ -3229,10 +3229,10 @@
         <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>122.6</v>
+        <v>1727.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>36.2</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>10.4</v>
+        <v>30.4</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>20.2</v>
@@ -3259,7 +3259,7 @@
       <c r="F34" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3271,8 +3271,8 @@
       <c r="J34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K34" s="8" t="n">
-        <v>2.4</v>
+      <c r="K34" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>20.4</v>
@@ -3293,28 +3293,28 @@
         <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>28.2</v>
+        <v>23.2</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>7886.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V34" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V34" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X34" s="8" t="n">
+      <c r="X34" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>1832.8</v>
+        <v>182.8</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>5.4</v>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>187.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>24.6</v>
@@ -3366,10 +3366,10 @@
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>21.3</v>
+        <v>29.3</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>3.6</v>
@@ -3387,22 +3387,22 @@
         <v>88.5</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>7.1</v>
+        <v>28.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>21.6</v>
+        <v>28.6</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>26.3</v>
+        <v>20.3</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>188.5</v>
+        <v>88.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3424,16 +3424,16 @@
         <v>28.6</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="F36" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>19</v>
+        <v>190.1</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>2.2</v>
@@ -3442,7 +3442,7 @@
         <v>12.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>20.6</v>
@@ -3451,7 +3451,7 @@
         <v>19.4</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>89</v>
@@ -3469,19 +3469,19 @@
         <v>25.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>822.5</v>
+        <v>72.3</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="V36" s="8" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="W36" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="W36" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>46.8</v>
+      <c r="X36" s="3" t="n">
+        <v>84.8</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>78.2</v>
@@ -3504,19 +3504,19 @@
         <v>11683.5</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1450.1</v>
+        <v>150.1</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>120.2</v>
+        <v>0.2</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>125.5</v>
+        <v>92.5</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>9224.1</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>12.6</v>
@@ -3531,10 +3531,10 @@
         <v>103.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1396.5</v>
+        <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>127.2</v>
+        <v>18.7</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>437.5</v>
@@ -3543,13 +3543,13 @@
         <v>14.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>129</v>
+        <v>139.6</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>126</v>
+        <v>1256</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>343.7</v>
@@ -3601,16 +3601,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>88.5</v>
+        <v>18.5</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>18.4</v>
+        <v>0.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
@@ -3634,25 +3634,25 @@
         <v>23.1</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>28.1</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>224.2</v>
+        <v>224.1</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>179.3</v>
+        <v>79.3</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>16.9</v>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>14001.8</v>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>11.8</v>
+        <v>400.8</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>31.8</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>19.5</v>
@@ -3683,44 +3683,44 @@
         <v>25.7</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>18.1</v>
+        <v>58.5</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
-        <v>29.9</v>
+        <v>13.9</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>10.5</v>
+        <v>20.5</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>12.8</v>
+      <c r="N39" s="8" t="n">
+        <v>88.40000000000001</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>30.4</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>25.1</v>
+        <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>23.6</v>
+        <v>22.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>534.5</v>
+        <v>54.5</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19.8</v>
@@ -3732,13 +3732,13 @@
         <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>27.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>175.4</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3756,8 +3756,8 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="8" t="n">
-        <v>444.6</v>
+      <c r="D40" s="3" t="n">
+        <v>9.1</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>90.2</v>
@@ -3766,10 +3766,10 @@
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>19</v>
+        <v>3.9</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>89</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.4</v>
@@ -3810,20 +3810,20 @@
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V40" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="W40" s="8" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="X40" s="8" t="n">
-        <v>217.2</v>
+      <c r="V40" s="8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W40" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>21.7</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>181.5</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>19.9</v>
+        <v>15.9</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3839,31 +3839,31 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>114.8</v>
+        <v>64.8</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>494.3</v>
+        <v>94.3</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="H41" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="K41" s="8" t="n">
-        <v>11.6</v>
+        <v>3.8</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.9</v>
@@ -3902,10 +3902,10 @@
         <v>22.2</v>
       </c>
       <c r="X41" s="8" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>19.6</v>
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>86.2</v>
+        <v>1464.5</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>98.8</v>
+        <v>32.8</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>17</v>
@@ -3945,7 +3945,7 @@
         <v>4.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0.2</v>
@@ -3971,14 +3971,14 @@
       <c r="R42" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>22.2</v>
+      <c r="S42" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="T42" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="U42" s="8" t="n">
-        <v>28.2</v>
+      <c r="U42" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>27.5</v>
@@ -3986,11 +3986,11 @@
       <c r="W42" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="X42" s="8" t="n">
-        <v>10.4</v>
+      <c r="X42" s="3" t="n">
+        <v>94.40000000000001</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>18708</v>
+        <v>182</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>8.699999999999999</v>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>44.1</v>
+        <v>34.1</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>32</v>
@@ -4030,7 +4030,7 @@
         <v>2.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>15.2</v>
@@ -4048,7 +4048,7 @@
         <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
@@ -4062,7 +4062,9 @@
       <c r="T43" s="3" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="U43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="V43" s="3" t="n">
         <v>23</v>
       </c>
@@ -4070,7 +4072,7 @@
         <v>22.4</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>0.3</v>
+        <v>53.1</v>
       </c>
       <c r="Y43" s="3" t="n">
         <v>182.8</v>
@@ -4092,7 +4094,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>121.6</v>
+        <v>141.6</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>23.9</v>
@@ -4109,11 +4111,11 @@
       <c r="H44" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I44" s="8" t="n">
-        <v>80.8</v>
+      <c r="I44" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>19.7</v>
@@ -4121,39 +4123,37 @@
       <c r="L44" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="N44" s="8" t="n">
-        <v>0.8</v>
+      <c r="M44" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>189</v>
+        <v>890.1</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>181.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v>822.3</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>20.2</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="W44" s="3" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4171,72 +4171,74 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>18841.1</v>
+        <v>168211.1</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>841.1</v>
+        <v>825.1</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>122.2</v>
+        <v>12.2</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>174</v>
+        <v>51.7</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>160.2</v>
+        <v>10.6</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>105.6</v>
+        <v>2637</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>169</v>
+        <v>183.3</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>2816.1</v>
+        <v>28</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>12180.4</v>
+        <v>1910.4</v>
       </c>
       <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="3" t="n">
-        <v>110109210619.1</v>
+        <v>10092105.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>204.1</v>
+        <v>34.2</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>16808.4</v>
+        <v>140.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1257.2</v>
+        <v>257.5</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>1291.7</v>
+        <v>129.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>18317.9</v>
+        <v>1382</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>44841.4</v>
+        <v>484</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="V45" s="3" t="inlineStr"/>
+        <v>11.2</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="W45" s="3" t="n">
-        <v>1122.2</v>
+        <v>182.2</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>924.7</v>
+        <v>24.7</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>81.5</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4252,7 +4254,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>511.7</v>
+        <v>311.7</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>29</v>
@@ -4263,20 +4265,20 @@
       <c r="F46" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>20.1</v>
+      <c r="G46" s="3" t="n">
+        <v>10.1</v>
       </c>
       <c r="H46" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="I46" s="8" t="n">
-        <v>122.6</v>
+      <c r="I46" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
@@ -4285,7 +4287,7 @@
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>60.5</v>
+        <v>20.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>89</v>
@@ -4294,7 +4296,7 @@
         <v>2.4</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>26.2</v>
+        <v>25.2</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>21.6</v>
@@ -4311,10 +4313,10 @@
       <c r="V46" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X46" s="8" t="n">
+      <c r="W46" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X46" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>83.7</v>
+        <v>43.7</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>31.2</v>
@@ -744,14 +744,14 @@
       <c r="E4" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>24.2</v>
+      <c r="F4" s="8" t="n">
+        <v>124.2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>91124.10000000001</v>
+        <v>27.4</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.1</v>
@@ -760,12 +760,12 @@
         <v>4.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="M4" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M4" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -793,9 +793,9 @@
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="W4" s="3" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="W4" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6.6</v>
+        <v>62.1</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>24.4</v>
@@ -830,11 +830,15 @@
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="n">
+        <v>25.4</v>
+      </c>
       <c r="L5" s="3" t="n">
         <v>19.1</v>
       </c>
@@ -847,21 +851,23 @@
       <c r="O5" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="P5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="n">
+        <v>2.3</v>
+      </c>
       <c r="Q5" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="S5" s="3" t="n">
+      <c r="S5" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>87.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>20.6</v>
@@ -892,7 +898,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>432.6</v>
+        <v>421.6</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>31.4</v>
@@ -900,7 +906,7 @@
       <c r="E6" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -910,12 +916,12 @@
         <v>17.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>18.5</v>
+        <v>2.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="K6" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K6" s="8" t="n">
         <v>0.6</v>
       </c>
       <c r="L6" s="3" t="n">
@@ -946,7 +952,7 @@
         <v>61.9</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>18.6</v>
+        <v>16</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>26.2</v>
@@ -982,9 +988,7 @@
       <c r="D7" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>1.7</v>
-      </c>
+      <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="n">
         <v>25</v>
       </c>
@@ -992,34 +996,34 @@
         <v>16</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>84.8</v>
+        <v>14.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>62</v>
+        <v>17.3</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>27.3</v>
+        <v>17.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>87.59999999999999</v>
+        <v>872.6</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>21.9</v>
+        <v>31.9</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>23.9</v>
@@ -1028,7 +1032,7 @@
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>52.1</v>
+        <v>152.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
@@ -1036,15 +1040,17 @@
       <c r="V7" s="3" t="n">
         <v>27.6</v>
       </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="8" t="n">
+      <c r="W7" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X7" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>727.9</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1060,18 +1066,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>297.6</v>
-      </c>
-      <c r="D8" s="3" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="D8" s="8" t="n">
         <v>32.6</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>19.8</v>
+        <v>4.1</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1090,7 +1096,7 @@
         <v>20</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>20.5</v>
@@ -1114,7 +1120,7 @@
         <v>95.40000000000001</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>24</v>
@@ -1123,12 +1129,14 @@
         <v>22.8</v>
       </c>
       <c r="X8" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>175.2</v>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="Y8" s="3" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1146,28 +1154,28 @@
         <v>166.6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>152.6</v>
+        <v>852.6</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>12.5</v>
+        <v>92.5</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>122.9</v>
+        <v>822.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>80.5</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>22.2</v>
+        <v>11.2</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>44</v>
+        <v>44.2</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>94.3</v>
@@ -1188,10 +1196,10 @@
         <v>138.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>117.3</v>
+        <v>1617.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1231.9</v>
+        <v>131.9</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>360.9</v>
@@ -1206,13 +1214,13 @@
         <v>113</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>12.9</v>
+        <v>129.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>114102.4</v>
+        <v>402.4</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>38.8</v>
+        <v>32.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1243,13 +1251,17 @@
         <v>12</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
+        <v>16.1</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="J10" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+        <v>3.1</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>18.9</v>
       </c>
@@ -1268,7 +1280,7 @@
       <c r="Q10" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1309,7 +1321,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2445.1</v>
+        <v>44.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>28.7</v>
@@ -1317,23 +1329,23 @@
       <c r="E11" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>85.2</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>20.1</v>
@@ -1342,13 +1354,13 @@
         <v>18.7</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>24.7</v>
+        <v>20.7</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>27.9</v>
@@ -1357,22 +1369,22 @@
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>31.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>85</v>
+        <v>850.1</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>58.7</v>
+        <v>5.7</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>25</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>2471.6</v>
+        <v>24.7</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>31.9</v>
+        <v>502.1</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>97.5</v>
@@ -1394,9 +1406,9 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>383.3</v>
-      </c>
-      <c r="D12" s="3" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="D12" s="8" t="n">
         <v>28.1</v>
       </c>
       <c r="E12" s="3" t="n">
@@ -1409,7 +1421,7 @@
         <v>8.5</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>2.9</v>
@@ -1418,7 +1430,7 @@
         <v>3.2</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>20.6</v>
@@ -1433,7 +1445,7 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.7</v>
+        <v>12.7</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>27.2</v>
@@ -1456,11 +1468,11 @@
       <c r="W12" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="X12" s="3" t="n">
+      <c r="X12" s="8" t="n">
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>97.7</v>
+        <v>1197.7</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>0.7</v>
@@ -1479,7 +1491,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>35.6</v>
+        <v>235.6</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>31.1</v>
@@ -1487,8 +1499,8 @@
       <c r="E13" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F13" s="8" t="n">
-        <v>35.5</v>
+      <c r="F13" s="3" t="n">
+        <v>25.5</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>11.3</v>
@@ -1548,7 +1560,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1564,7 +1576,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>32.4</v>
+        <v>37.4</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>32.5</v>
@@ -1579,20 +1591,22 @@
         <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="n">
+        <v>3.3</v>
+      </c>
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="3" t="n">
-        <v>28.7</v>
+      <c r="M14" s="8" t="n">
+        <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>20.8</v>
@@ -1601,7 +1615,7 @@
         <v>89.90000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>30.6</v>
@@ -1615,7 +1629,7 @@
       <c r="T14" s="3" t="n">
         <v>50.9</v>
       </c>
-      <c r="U14" s="3" t="n">
+      <c r="U14" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="V14" s="3" t="n">
@@ -1624,7 +1638,7 @@
       <c r="W14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="3" t="n">
+      <c r="X14" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
@@ -1647,13 +1661,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>43.3</v>
+        <v>143.3</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>20.2</v>
+      <c r="E15" s="8" t="n">
+        <v>2.8</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>24.9</v>
@@ -1662,7 +1676,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>89.8</v>
+        <v>19.8</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>1.9</v>
@@ -1671,13 +1685,13 @@
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>16.8</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="M15" s="3" t="n">
-        <v>19.1</v>
+      <c r="M15" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>21.3</v>
@@ -1701,22 +1715,22 @@
         <v>63.8</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="V15" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="V15" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X15" s="3" t="n">
+      <c r="X15" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>74</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1732,10 +1746,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>199.2</v>
+        <v>1992.8</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>19249.9</v>
+        <v>149.9</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>99.09999999999999</v>
@@ -1744,31 +1758,29 @@
         <v>124.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>50.8</v>
+        <v>508.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>8.1</v>
+        <v>11.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>16</v>
-      </c>
+        <v>115.8</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="3" t="n">
-        <v>11.2</v>
+        <v>1.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>924.6</v>
+        <v>194.6</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>105.8</v>
+        <v>105.2</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>444.8</v>
+        <v>444.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>12.9</v>
@@ -1777,10 +1789,10 @@
         <v>142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>142.5</v>
+        <v>1042.5</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>368.7</v>
@@ -1795,7 +1807,7 @@
         <v>115.1</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>137.5</v>
+        <v>2.5</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>455.1</v>
@@ -1817,7 +1829,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>39.8</v>
+        <v>399.8</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>30</v>
@@ -1829,20 +1841,22 @@
         <v>24.9</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>18.1</v>
+        <v>28.1</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>3.2</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>11551.5</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>18.9</v>
@@ -1851,7 +1865,7 @@
         <v>21</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>2.6</v>
@@ -1859,14 +1873,14 @@
       <c r="Q17" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R17" s="8" t="n">
-        <v>8224</v>
-      </c>
-      <c r="S17" s="8" t="n">
+      <c r="R17" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="S17" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>73.7</v>
+        <v>173.7</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>10.6</v>
@@ -1875,7 +1889,7 @@
         <v>24.2</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="X17" s="3" t="n">
         <v>27.5</v>
@@ -1900,46 +1914,46 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.5</v>
+        <v>431.1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>40.8</v>
+        <v>30.8</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>19</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>14.9</v>
+        <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.1</v>
+        <v>14.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>24.9</v>
+        <v>13.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>19.6</v>
+        <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>27.7</v>
+        <v>20.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.9</v>
+        <v>13.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>28.6</v>
@@ -1951,7 +1965,7 @@
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>1.2</v>
+        <v>63.1</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>14.4</v>
@@ -1959,11 +1973,11 @@
       <c r="V18" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="8" t="n">
-        <v>50.6</v>
+      <c r="W18" s="3" t="n">
+        <v>25.6</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>92.09999999999999</v>
@@ -1985,7 +1999,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>433.6</v>
+        <v>2223.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>32.5</v>
@@ -2006,16 +2020,16 @@
         <v>2.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>91.5</v>
+        <v>21.5</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>28.2</v>
+      <c r="M19" s="8" t="n">
+        <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>20</v>
@@ -2027,7 +2041,7 @@
         <v>2.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>21.8</v>
+        <v>31.8</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>24.2</v>
@@ -2053,7 +2067,9 @@
       <c r="Y19" s="3" t="n">
         <v>81.2</v>
       </c>
-      <c r="Z19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2068,7 +2084,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>956.8</v>
+        <v>25.6</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>27.2</v>
@@ -2080,7 +2096,7 @@
         <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>1.8</v>
@@ -2088,9 +2104,11 @@
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="K20" s="3" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>20</v>
@@ -2102,31 +2120,31 @@
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>289</v>
+        <v>89</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>21.5</v>
+        <v>25.5</v>
+      </c>
+      <c r="R20" s="8" t="n">
+        <v>241.5</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>707.2</v>
+        <v>70.7</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>106.1</v>
+        <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>21.2</v>
@@ -2177,11 +2195,11 @@
       <c r="K21" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>12.3</v>
+        <v>17.3</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>18.8</v>
@@ -2190,7 +2208,7 @@
         <v>86.7</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>30.1</v>
@@ -2202,10 +2220,10 @@
         <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v>8.9</v>
+        <v>31</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.3</v>
@@ -2217,7 +2235,7 @@
         <v>25.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>850.8</v>
+        <v>85</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>14.5</v>
@@ -2236,19 +2254,19 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>374.1</v>
-      </c>
-      <c r="D22" s="3" t="n">
+        <v>2374.6</v>
+      </c>
+      <c r="D22" s="8" t="n">
         <v>31.8</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>24.5</v>
+        <v>17.2</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>247.5</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>84.59999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>1.5</v>
@@ -2265,8 +2283,8 @@
       <c r="L22" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M22" s="3" t="n">
-        <v>16.2</v>
+      <c r="M22" s="8" t="n">
+        <v>26.2</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>17.5</v>
@@ -2287,13 +2305,13 @@
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>56.4</v>
+        <v>256.4</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="3" t="n">
-        <v>21.5</v>
+      <c r="V22" s="8" t="n">
+        <v>21.2</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>19.5</v>
@@ -2321,10 +2339,10 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1925.5</v>
+        <v>192.5</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>155.1</v>
+        <v>153.1</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>92.8</v>
@@ -2333,7 +2351,7 @@
         <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>605.9</v>
+        <v>60.5</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>85.59999999999999</v>
@@ -2342,10 +2360,10 @@
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>15.5</v>
+        <v>25.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>495.3</v>
+        <v>49.5</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>95.2</v>
@@ -2363,34 +2381,34 @@
         <v>113.7</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>14.6</v>
+        <v>146.2</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1143.1</v>
+        <v>114.3</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>295.2</v>
+        <v>2895.2</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>85.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>22.2</v>
+        <v>122.2</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>21</v>
+        <v>110.7</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>226.7</v>
+        <v>126.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>1411</v>
+        <v>411</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>27.1</v>
+        <v>0.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2406,22 +2424,22 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>28.5</v>
+        <v>1398.5</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>24.6</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>1.7</v>
+        <v>12</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>67.59999999999999</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2439,7 +2457,7 @@
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>19.3</v>
+        <v>12.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>87.40000000000001</v>
@@ -2448,7 +2466,7 @@
         <v>2.7</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>2.9</v>
+        <v>29.2</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>22.9</v>
@@ -2460,7 +2478,7 @@
         <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>24.4</v>
@@ -2471,7 +2489,9 @@
       <c r="X24" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Y24" s="3" t="n">
+        <v>82.2</v>
+      </c>
       <c r="Z24" s="3" t="n">
         <v>5.4</v>
       </c>
@@ -2489,15 +2509,15 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>374</v>
+        <v>2374</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>12.1</v>
+        <v>32.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F25" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F25" s="8" t="n">
         <v>25.7</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2507,7 +2527,7 @@
         <v>18</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>3.6</v>
@@ -2525,25 +2545,25 @@
         <v>20.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>12.2</v>
+        <v>18.2</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>24</v>
+        <v>24.3</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>25.9</v>
+        <v>22.9</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>56.9</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>1.8</v>
+        <v>19.7</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>24.2</v>
@@ -2551,14 +2571,14 @@
       <c r="W25" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="3" t="n">
+      <c r="X25" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>174.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>7.5</v>
+        <v>17.2</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2574,7 +2594,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>329.2</v>
+        <v>329.8</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>30.8</v>
@@ -2589,13 +2609,13 @@
         <v>12.2</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J26" s="8" t="n">
-        <v>25.6</v>
+      <c r="J26" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.3</v>
@@ -2607,7 +2627,7 @@
         <v>17.6</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>89.2</v>
+        <v>19.2</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>87</v>
@@ -2622,13 +2642,13 @@
         <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>80</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>24.2</v>
@@ -2636,10 +2656,12 @@
       <c r="W26" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="X26" s="3" t="n">
+      <c r="X26" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Y26" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
       <c r="Z26" s="3" t="n">
         <v>17.6</v>
       </c>
@@ -2657,10 +2679,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>354.8</v>
+        <v>1354.4</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>19.4</v>
@@ -2671,11 +2693,11 @@
       <c r="G27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>2.9</v>
@@ -2693,7 +2715,7 @@
         <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>87.5</v>
+        <v>88.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>2.9</v>
@@ -2710,11 +2732,11 @@
       <c r="T27" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U27" s="3" t="n">
-        <v>10.4</v>
+      <c r="U27" s="8" t="n">
+        <v>10.6</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>63.4</v>
+        <v>23.2</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>20.8</v>
@@ -2723,7 +2745,7 @@
         <v>23</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>84.8</v>
+        <v>802.1</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>5.4</v>
@@ -2742,7 +2764,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.8</v>
+        <v>389.3</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>29.8</v>
@@ -2766,7 +2788,7 @@
         <v>3.8</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>20.6</v>
@@ -2796,13 +2818,13 @@
         <v>64.90000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V28" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V28" s="8" t="n">
         <v>26</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>956.1</v>
+        <v>23.6</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>27.6</v>
@@ -2811,7 +2833,7 @@
         <v>82</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2830,28 +2852,28 @@
         <v>20.8</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>49.4</v>
+        <v>29.4</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>613.1</v>
+        <v>20.3</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.1</v>
+        <v>19.1</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>20.3</v>
@@ -2859,14 +2881,14 @@
       <c r="M29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>28.6</v>
@@ -2874,16 +2896,16 @@
       <c r="R29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="8" t="n">
+      <c r="S29" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>62.4</v>
+        <v>62.6</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="W29" s="3" t="n">
@@ -2912,22 +2934,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11856.4</v>
+        <v>1856.4</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>150.5</v>
+        <v>150.3</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>97.8</v>
+        <v>91.2</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>124.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>52.5</v>
+        <v>152.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>9.1</v>
+        <v>191.7</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>10</v>
@@ -2939,13 +2961,13 @@
         <v>25.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>929.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>103.4</v>
+        <v>103.2</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>441.9</v>
@@ -2954,7 +2976,7 @@
         <v>13.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>238.5</v>
+        <v>138.5</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>113.7</v>
@@ -2966,7 +2988,7 @@
         <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>6.4</v>
+        <v>16.4</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>123.1</v>
@@ -2975,10 +2997,10 @@
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>61.3</v>
+        <v>124.3</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>43.9</v>
+        <v>399.8</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>32.6</v>
@@ -2997,16 +3019,16 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>33.4</v>
+        <v>37.1</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>30.8</v>
+        <v>20.1</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>9.6</v>
+        <v>19.6</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>94.8</v>
+        <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>10.5</v>
@@ -3015,12 +3037,14 @@
         <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
+        <v>13.2</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L31" s="3" t="n">
         <v>19.9</v>
       </c>
@@ -3042,28 +3066,30 @@
       <c r="R31" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="S31" s="3" t="n">
+      <c r="S31" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="V31" s="8" t="n">
-        <v>824.6</v>
+      <c r="V31" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>24.9</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="Z31" s="3" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>6.5</v>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3078,31 +3104,31 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>143.7</v>
+        <v>45.7</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>12.8</v>
+        <v>352.8</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="G32" s="3" t="n">
+      <c r="F32" s="8" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="G32" s="8" t="n">
         <v>12.6</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>20.6</v>
@@ -3111,13 +3137,13 @@
         <v>19.3</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>31</v>
@@ -3132,22 +3158,22 @@
         <v>56.6</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V32" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="V32" s="8" t="n">
         <v>28.2</v>
       </c>
       <c r="W32" s="8" t="n">
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>169.1</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>111.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3163,10 +3189,10 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>310.1</v>
-      </c>
-      <c r="D33" s="8" t="n">
-        <v>14.1</v>
+        <v>397.9</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>33.7</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>19.8</v>
@@ -3187,7 +3213,7 @@
         <v>5.5</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.9</v>
@@ -3207,19 +3233,19 @@
       <c r="Q33" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="R33" s="8" t="n">
-        <v>38.9</v>
+      <c r="R33" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>47.7</v>
+        <v>147.7</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="V33" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="W33" s="3" t="n">
@@ -3229,10 +3255,10 @@
         <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1727.6</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>7.4</v>
+        <v>17.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3248,7 +3274,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>36.2</v>
+        <v>1362.4</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>30.4</v>
@@ -3263,16 +3289,16 @@
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>12.4</v>
+        <v>1.2</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>20.4</v>
@@ -3304,7 +3330,7 @@
       <c r="U34" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V34" s="8" t="n">
+      <c r="V34" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="W34" s="3" t="n">
@@ -3314,7 +3340,7 @@
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>182.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>5.4</v>
@@ -3348,7 +3374,7 @@
         <v>3.9</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>1.8</v>
+        <v>18.7</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>0.3</v>
@@ -3360,13 +3386,13 @@
         <v>9</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>29.3</v>
+        <v>20</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>85.40000000000001</v>
@@ -3387,10 +3413,10 @@
         <v>88.5</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>28.4</v>
+        <v>3.1</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>28.6</v>
+        <v>21.6</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>20.3</v>
@@ -3420,7 +3446,7 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="E36" s="3" t="n">
@@ -3432,17 +3458,17 @@
       <c r="G36" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H36" s="3" t="n">
-        <v>190.1</v>
+      <c r="H36" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>20.6</v>
@@ -3451,7 +3477,7 @@
         <v>19.4</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>89</v>
@@ -3474,19 +3500,21 @@
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="8" t="n">
-        <v>58</v>
+      <c r="V36" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>84.8</v>
+        <v>24.8</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>78.2</v>
       </c>
-      <c r="Z36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="n">
+        <v>6.9</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3501,19 +3529,19 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>11683.5</v>
+        <v>168.3</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>150.1</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.2</v>
+        <v>100.9</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>92.5</v>
+        <v>125.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>49.2</v>
+        <v>149.2</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.40000000000001</v>
@@ -3525,7 +3553,7 @@
         <v>15.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>10.2</v>
+        <v>102.8</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.5</v>
@@ -3534,7 +3562,7 @@
         <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>18.7</v>
+        <v>107.2</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>437.5</v>
@@ -3549,7 +3577,7 @@
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1256</v>
+        <v>126</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>343.7</v>
@@ -3586,7 +3614,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>336.7</v>
+        <v>2326.7</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>30</v>
@@ -3594,7 +3622,7 @@
       <c r="E38" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="3" t="n">
+      <c r="F38" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3607,7 +3635,7 @@
         <v>2.5</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0.1</v>
@@ -3616,10 +3644,10 @@
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>19.3</v>
+        <v>1.9</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>28.4</v>
+        <v>21.4</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>87.5</v>
@@ -3634,19 +3662,19 @@
         <v>23.1</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>22.2</v>
+        <v>25.2</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>28.1</v>
+        <v>13.1</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>224.1</v>
+        <v>22.4</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>25.4</v>
@@ -3655,7 +3683,7 @@
         <v>79.3</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3671,7 +3699,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>400.8</v>
+        <v>1400.8</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>31.8</v>
@@ -3682,13 +3710,15 @@
       <c r="F39" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="G39" s="8" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="H39" s="8" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="I39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>2.5</v>
+      </c>
       <c r="J39" s="3" t="n">
         <v>13.9</v>
       </c>
@@ -3702,22 +3732,22 @@
         <v>19.5</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>88.40000000000001</v>
+        <v>22</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>30.4</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>22.6</v>
+        <v>23.6</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>54.5</v>
@@ -3728,7 +3758,7 @@
       <c r="V39" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="W39" s="3" t="n">
+      <c r="W39" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3756,20 +3786,20 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="3" t="n">
-        <v>9.1</v>
+      <c r="D40" s="8" t="n">
+        <v>84.09999999999999</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="F40" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F40" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>3.9</v>
+        <v>13.9</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.4</v>
@@ -3787,7 +3817,7 @@
         <v>19.1</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>22.2</v>
+        <v>24.2</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>88</v>
@@ -3810,20 +3840,20 @@
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V40" s="8" t="n">
-        <v>8.300000000000001</v>
+      <c r="V40" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>181.5</v>
+        <v>85.5</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>15.9</v>
+        <v>81.3</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3839,15 +3869,15 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>64.8</v>
+        <v>244.8</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>94.3</v>
+        <v>8.9</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F41" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F41" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
@@ -3857,7 +3887,7 @@
         <v>17.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>3.8</v>
@@ -3901,14 +3931,14 @@
       <c r="W41" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="X41" s="8" t="n">
+      <c r="X41" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>74</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3924,7 +3954,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1464.5</v>
+        <v>116.4</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>32.8</v>
@@ -3935,7 +3965,7 @@
       <c r="F42" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -3951,7 +3981,7 @@
         <v>0.2</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>16.1</v>
@@ -3963,7 +3993,7 @@
         <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>12.1</v>
+        <v>2.1</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>30.8</v>
@@ -3971,11 +4001,11 @@
       <c r="R42" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="S42" s="8" t="n">
-        <v>28.2</v>
+      <c r="S42" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>22.2</v>
@@ -3984,16 +4014,16 @@
         <v>27.5</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>25.8</v>
+        <v>23.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>27.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>182</v>
+        <v>24.4</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>87</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4009,18 +4039,18 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>34.1</v>
+        <v>2341.3</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>32</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>18.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="G43" s="3" t="n">
+      <c r="G43" s="8" t="n">
         <v>13.4</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4041,14 +4071,14 @@
       <c r="M43" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="N43" s="3" t="n">
+      <c r="N43" s="8" t="n">
         <v>19.4</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>188.1</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0.2</v>
+        <v>12.5</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
@@ -4056,14 +4086,14 @@
       <c r="R43" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="S43" s="3" t="n">
+      <c r="S43" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>0.5</v>
+        <v>5.7</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>23</v>
@@ -4072,10 +4102,10 @@
         <v>22.4</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>53.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>182.8</v>
+        <v>82.8</v>
       </c>
       <c r="Z43" s="3" t="n">
         <v>14.6</v>
@@ -4102,7 +4132,7 @@
       <c r="E44" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="G44" s="3" t="n">
@@ -4115,22 +4145,22 @@
         <v>0.8</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="L44" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>20.1</v>
+      <c r="M44" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N44" s="8" t="n">
+        <v>4.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>890.1</v>
+        <v>240.1</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>2.4</v>
@@ -4145,15 +4175,17 @@
         <v>22.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V44" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="V44" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="n">
+        <v>20.2</v>
+      </c>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4171,71 +4203,71 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>168211.1</v>
+        <v>1.8</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>825.1</v>
+        <v>174</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>12.2</v>
+        <v>113.8</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>51.7</v>
+        <v>144</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>10.6</v>
+        <v>60.2</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>2637</v>
+        <v>105.6</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>183.3</v>
+        <v>13.3</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1910.4</v>
-      </c>
-      <c r="M45" s="3" t="inlineStr"/>
+        <v>110.4</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>109.2</v>
+      </c>
       <c r="N45" s="3" t="n">
-        <v>10092105.9</v>
+        <v>1218.1</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>34.2</v>
+        <v>534.4</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>140.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>257.5</v>
+        <v>157.5</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>129.2</v>
+        <v>129.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>1382</v>
+        <v>138.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>11.2</v>
+        <v>1121.5</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>12.2</v>
+        <v>145.5</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>182.2</v>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v>24.7</v>
-      </c>
+        <v>231.2</v>
+      </c>
+      <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>81.5</v>
+        <v>48390.4</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>5.8</v>
@@ -4260,16 +4292,16 @@
         <v>29</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>18.9</v>
+        <v>1.8</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>10.1</v>
+      <c r="G46" s="8" t="n">
+        <v>4.1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>17.6</v>
+        <v>167.6</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>2.2</v>
@@ -4277,9 +4309,7 @@
       <c r="J46" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
       </c>
@@ -4290,13 +4320,13 @@
         <v>20.2</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>89</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>25.2</v>
+        <v>26.2</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>21.6</v>
@@ -4313,10 +4343,10 @@
       <c r="V46" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="X46" s="3" t="n">
+      <c r="X46" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -744,8 +735,8 @@
       <c r="E4" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F4" s="8" t="n">
-        <v>124.2</v>
+      <c r="F4" s="3" t="n">
+        <v>24.2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14</v>
@@ -765,7 +756,7 @@
       <c r="L4" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -795,7 +786,7 @@
       <c r="V4" s="3" t="n">
         <v>27.7</v>
       </c>
-      <c r="W4" s="8" t="n">
+      <c r="W4" s="3" t="n">
         <v>24</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -830,14 +821,14 @@
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>25.4</v>
+        <v>25.8</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>19.1</v>
@@ -860,7 +851,7 @@
       <c r="R5" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
@@ -906,7 +897,7 @@
       <c r="E6" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -921,8 +912,8 @@
       <c r="J6" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K6" s="8" t="n">
-        <v>0.6</v>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20.3</v>
@@ -995,7 +986,7 @@
       <c r="G7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I7" s="3" t="n">
@@ -1005,7 +996,7 @@
         <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>17.3</v>
@@ -1013,11 +1004,11 @@
       <c r="M7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>872.6</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
@@ -1032,7 +1023,7 @@
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>152.1</v>
+        <v>52.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
@@ -1066,9 +1057,9 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="D8" s="8" t="n">
+        <v>297.2</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>32.6</v>
       </c>
       <c r="E8" s="3" t="n">
@@ -1077,7 +1068,7 @@
       <c r="F8" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1132,7 +1123,7 @@
         <v>27.8</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>175.2</v>
+        <v>75.2</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>27</v>
@@ -1154,13 +1145,13 @@
         <v>166.6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>852.6</v>
+        <v>252.6</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>92.5</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>822.5</v>
+        <v>122.5</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>6</v>
@@ -1175,7 +1166,7 @@
         <v>15.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>44.2</v>
+        <v>44</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>94.3</v>
@@ -1196,7 +1187,7 @@
         <v>138.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1617.3</v>
+        <v>117.3</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>131.9</v>
@@ -1220,7 +1211,7 @@
         <v>402.4</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>32.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1265,10 +1256,10 @@
       <c r="L10" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="8" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="N10" s="8" t="n">
+      <c r="M10" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="N10" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="O10" s="3" t="n">
@@ -1280,7 +1271,7 @@
       <c r="Q10" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="R10" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1329,7 +1320,7 @@
       <c r="E11" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1369,7 +1360,7 @@
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>850.1</v>
@@ -1408,7 +1399,7 @@
       <c r="C12" s="3" t="n">
         <v>38.3</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="3" t="n">
         <v>28.1</v>
       </c>
       <c r="E12" s="3" t="n">
@@ -1421,7 +1412,7 @@
         <v>8.5</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>2.9</v>
@@ -1445,7 +1436,7 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>12.7</v>
+        <v>2.7</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>27.2</v>
@@ -1468,11 +1459,11 @@
       <c r="W12" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="X12" s="8" t="n">
+      <c r="X12" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>1197.7</v>
+        <v>97.7</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>0.7</v>
@@ -1491,7 +1482,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>235.6</v>
+        <v>35.6</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>31.1</v>
@@ -1605,7 +1596,7 @@
       <c r="L14" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1629,7 +1620,7 @@
       <c r="T14" s="3" t="n">
         <v>50.9</v>
       </c>
-      <c r="U14" s="8" t="n">
+      <c r="U14" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="V14" s="3" t="n">
@@ -1638,7 +1629,7 @@
       <c r="W14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
@@ -1661,13 +1652,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>143.3</v>
+        <v>43.3</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="8" t="n">
-        <v>2.8</v>
+      <c r="E15" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>24.9</v>
@@ -1690,8 +1681,8 @@
       <c r="L15" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="M15" s="8" t="n">
-        <v>29.1</v>
+      <c r="M15" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>21.3</v>
@@ -1717,13 +1708,13 @@
       <c r="U15" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="V15" s="8" t="n">
+      <c r="V15" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X15" s="8" t="n">
+      <c r="X15" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
@@ -1746,7 +1737,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1992.8</v>
+        <v>992.7</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>149.9</v>
@@ -1761,20 +1752,20 @@
         <v>508.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>115.8</v>
+        <v>15.8</v>
       </c>
       <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>194.6</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>105.2</v>
@@ -1792,7 +1783,7 @@
         <v>123</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1042.5</v>
+        <v>142.5</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>368.7</v>
@@ -1829,7 +1820,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>399.8</v>
+        <v>39.8</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>30</v>
@@ -1841,10 +1832,10 @@
         <v>24.9</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>28.1</v>
+        <v>18.1</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>2.2</v>
@@ -1852,10 +1843,10 @@
       <c r="J17" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K17" s="8" t="n">
-        <v>11551.5</v>
-      </c>
-      <c r="L17" s="8" t="n">
+      <c r="K17" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L17" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="M17" s="3" t="n">
@@ -1880,7 +1871,7 @@
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>173.7</v>
+        <v>73.7</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>10.6</v>
@@ -1926,13 +1917,13 @@
         <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>11.3</v>
+        <v>11.8</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>14.2</v>
+        <v>17.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>4</v>
@@ -1944,16 +1935,16 @@
         <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>20.8</v>
+        <v>17.7</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>13.3</v>
+        <v>19.3</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>87</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>28.6</v>
@@ -1974,7 +1965,7 @@
         <v>26</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>25.6</v>
+        <v>25</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>31</v>
@@ -1999,7 +1990,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2223.4</v>
+        <v>223.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>32.5</v>
@@ -2011,10 +2002,10 @@
         <v>25.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>18.4</v>
+        <v>1.4</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.6</v>
@@ -2028,7 +2019,7 @@
       <c r="L19" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2099,16 +2090,16 @@
         <v>7.4</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>24.4</v>
+        <v>24</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>20</v>
@@ -2128,8 +2119,8 @@
       <c r="Q20" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R20" s="8" t="n">
-        <v>241.5</v>
+      <c r="R20" s="3" t="n">
+        <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
@@ -2195,7 +2186,7 @@
       <c r="K21" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="L21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -2220,7 +2211,7 @@
         <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
@@ -2238,7 +2229,7 @@
         <v>85</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2254,18 +2245,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2374.6</v>
-      </c>
-      <c r="D22" s="8" t="n">
+        <v>374</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>31.8</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F22" s="8" t="n">
-        <v>247.5</v>
-      </c>
-      <c r="G22" s="8" t="n">
+      <c r="F22" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2283,8 +2274,8 @@
       <c r="L22" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M22" s="8" t="n">
-        <v>26.2</v>
+      <c r="M22" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>17.5</v>
@@ -2305,12 +2296,12 @@
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>256.4</v>
+        <v>56.4</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="W22" s="3" t="n">
@@ -2339,7 +2330,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>192.5</v>
+        <v>1925.5</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>153.1</v>
@@ -2351,19 +2342,19 @@
         <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>25.5</v>
+        <v>125.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>95.2</v>
@@ -2378,7 +2369,7 @@
         <v>437.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>113.7</v>
+        <v>13.7</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>146.2</v>
@@ -2390,7 +2381,7 @@
         <v>119</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2895.2</v>
+        <v>295.2</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>85.40000000000001</v>
@@ -2405,10 +2396,10 @@
         <v>126.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>411</v>
+        <v>11</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2424,7 +2415,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1398.5</v>
+        <v>38.5</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>30.6</v>
@@ -2438,8 +2429,8 @@
       <c r="G24" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H24" s="8" t="n">
-        <v>67.59999999999999</v>
+      <c r="H24" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2457,7 +2448,7 @@
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>12.3</v>
+        <v>19.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>87.40000000000001</v>
@@ -2478,7 +2469,7 @@
         <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17.1</v>
+        <v>1.7</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>24.4</v>
@@ -2509,15 +2500,15 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2374</v>
+        <v>374</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>32.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F25" s="8" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F25" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2548,7 +2539,7 @@
         <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>18.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>31.3</v>
@@ -2557,7 +2548,7 @@
         <v>24.3</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>22.9</v>
+        <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>56.9</v>
@@ -2571,14 +2562,14 @@
       <c r="W25" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>174.8</v>
+        <v>74.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2648,7 +2639,7 @@
         <v>80</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>24.2</v>
@@ -2656,14 +2647,14 @@
       <c r="W26" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="X26" s="8" t="n">
+      <c r="X26" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2679,7 +2670,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1354.4</v>
+        <v>354.8</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>2.2</v>
@@ -2691,13 +2682,13 @@
         <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>2.9</v>
@@ -2715,7 +2706,7 @@
         <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>88.5</v>
+        <v>87.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>2.9</v>
@@ -2732,7 +2723,7 @@
       <c r="T27" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U27" s="8" t="n">
+      <c r="U27" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="V27" s="3" t="n">
@@ -2820,7 +2811,7 @@
       <c r="U28" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="V28" s="8" t="n">
+      <c r="V28" s="3" t="n">
         <v>26</v>
       </c>
       <c r="W28" s="3" t="n">
@@ -2861,19 +2852,19 @@
         <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.7</v>
+        <v>11.7</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>20.3</v>
@@ -2881,7 +2872,7 @@
       <c r="M29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="8" t="n">
+      <c r="N29" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="O29" s="3" t="n">
@@ -2905,7 +2896,7 @@
       <c r="U29" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="V29" s="8" t="n">
+      <c r="V29" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="W29" s="3" t="n">
@@ -2934,7 +2925,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1856.4</v>
+        <v>1856</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>150.3</v>
@@ -2946,10 +2937,10 @@
         <v>124.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>152.5</v>
+        <v>52.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>191.7</v>
+        <v>91.7</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>10</v>
@@ -2961,7 +2952,7 @@
         <v>25.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>29.6</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>93.2</v>
@@ -2988,7 +2979,7 @@
         <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>16.4</v>
+        <v>6.4</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>123.1</v>
@@ -3022,7 +3013,7 @@
         <v>37.1</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>20.1</v>
+        <v>30.1</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>19.6</v>
@@ -3033,14 +3024,14 @@
       <c r="G31" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H31" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>13.2</v>
+        <v>3.2</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>0.1</v>
@@ -3066,11 +3057,11 @@
       <c r="R31" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="S31" s="8" t="n">
+      <c r="S31" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>66</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>1.2</v>
@@ -3104,25 +3095,25 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>352.8</v>
+        <v>43.7</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>32.8</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F32" s="8" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="G32" s="8" t="n">
+      <c r="F32" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G32" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.4</v>
@@ -3136,7 +3127,7 @@
       <c r="M32" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N32" s="8" t="n">
+      <c r="N32" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="O32" s="3" t="n">
@@ -3160,17 +3151,17 @@
       <c r="U32" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="V32" s="8" t="n">
+      <c r="V32" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>11.8</v>
@@ -3189,7 +3180,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>397.9</v>
+        <v>397</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>33.7</v>
@@ -3240,12 +3231,12 @@
         <v>23.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>147.7</v>
+        <v>47.7</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V33" s="8" t="n">
+      <c r="V33" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="W33" s="3" t="n">
@@ -3258,7 +3249,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3274,7 +3265,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1362.4</v>
+        <v>362.4</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>30.4</v>
@@ -3289,7 +3280,7 @@
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.2</v>
@@ -3340,7 +3331,7 @@
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>5.4</v>
@@ -3386,13 +3377,13 @@
         <v>9</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>20</v>
+        <v>21.5</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>85.40000000000001</v>
@@ -3446,7 +3437,7 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="E36" s="3" t="n">
@@ -3458,7 +3449,7 @@
       <c r="G36" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="H36" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
@@ -3529,7 +3520,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>168.3</v>
+        <v>1683.5</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>150.1</v>
@@ -3541,7 +3532,7 @@
         <v>125.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>149.2</v>
+        <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.40000000000001</v>
@@ -3553,7 +3544,7 @@
         <v>15.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>102.8</v>
+        <v>10.2</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.5</v>
@@ -3614,7 +3605,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2326.7</v>
+        <v>336.7</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>30</v>
@@ -3622,7 +3613,7 @@
       <c r="E38" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F38" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3632,7 +3623,7 @@
         <v>18.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.5</v>
+        <v>22.5</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.1</v>
@@ -3644,7 +3635,7 @@
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>1.9</v>
+        <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>21.4</v>
@@ -3699,7 +3690,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1400.8</v>
+        <v>400.8</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>31.8</v>
@@ -3720,7 +3711,7 @@
         <v>2.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
@@ -3731,7 +3722,7 @@
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="8" t="n">
+      <c r="N39" s="3" t="n">
         <v>22</v>
       </c>
       <c r="O39" s="3" t="n">
@@ -3758,7 +3749,7 @@
       <c r="V39" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="W39" s="8" t="n">
+      <c r="W39" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3786,20 +3777,20 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="8" t="n">
-        <v>84.09999999999999</v>
+      <c r="D40" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>129</v>
+        <v>3.9</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.4</v>
@@ -3808,7 +3799,7 @@
         <v>0.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>20.4</v>
@@ -3869,19 +3860,19 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>244.8</v>
+        <v>448.8</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>17.4</v>
@@ -3954,7 +3945,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>116.4</v>
+        <v>64</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>32.8</v>
@@ -3965,7 +3956,7 @@
       <c r="F42" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="G42" s="8" t="n">
+      <c r="G42" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -3981,7 +3972,7 @@
         <v>0.2</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>17.8</v>
+        <v>17.2</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>16.1</v>
@@ -4005,7 +3996,7 @@
         <v>22.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>22.2</v>
@@ -4039,18 +4030,18 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2341.3</v>
+        <v>341.3</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="E43" s="8" t="n">
-        <v>88.59999999999999</v>
+      <c r="E43" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="G43" s="8" t="n">
+      <c r="G43" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4071,14 +4062,14 @@
       <c r="M43" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="N43" s="8" t="n">
+      <c r="N43" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>188.1</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
@@ -4086,7 +4077,7 @@
       <c r="R43" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="S43" s="8" t="n">
+      <c r="S43" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="T43" s="3" t="n">
@@ -4099,7 +4090,7 @@
         <v>23</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>22.4</v>
+        <v>21.4</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.300000000000001</v>
@@ -4108,7 +4099,7 @@
         <v>82.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4132,7 +4123,7 @@
       <c r="E44" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F44" s="8" t="n">
+      <c r="F44" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="G44" s="3" t="n">
@@ -4148,16 +4139,16 @@
         <v>0.6</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="L44" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L44" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="N44" s="8" t="n">
-        <v>4.1</v>
+      <c r="N44" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>240.1</v>
@@ -4178,9 +4169,9 @@
         <v>81</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="V44" s="8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="V44" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="W44" s="3" t="n">
@@ -4230,19 +4221,19 @@
         <v>30</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>110.4</v>
+        <v>116.4</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>109.2</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1218.1</v>
+        <v>121.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>534.4</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>140.4</v>
+        <v>14.2</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>157.5</v>
@@ -4251,23 +4242,23 @@
         <v>129.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>138.5</v>
+        <v>137.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>424</v>
+        <v>14</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>1121.5</v>
+        <v>71.5</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>145.5</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>231.2</v>
+        <v>131.6</v>
       </c>
       <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>48390.4</v>
+        <v>489</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>5.8</v>
@@ -4286,22 +4277,22 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>311.7</v>
+        <v>11.7</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>29</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>1.8</v>
+        <v>18.9</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H46" s="8" t="n">
-        <v>167.6</v>
+      <c r="G46" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>2.2</v>
@@ -4309,7 +4300,9 @@
       <c r="J46" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
       </c>
@@ -4320,7 +4313,7 @@
         <v>20.2</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>2.4</v>
@@ -4343,10 +4336,10 @@
       <c r="V46" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="8" t="n">
+      <c r="W46" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="X46" s="8" t="n">
+      <c r="X46" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
@@ -1145,7 +1145,7 @@
         <v>166.6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>252.6</v>
+        <v>152.6</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>92.5</v>
@@ -1166,7 +1166,7 @@
         <v>15.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>44</v>
+        <v>44.2</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>94.3</v>
@@ -1178,7 +1178,7 @@
         <v>96.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>440.9</v>
+        <v>22.2</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>12.9</v>
@@ -1211,7 +1211,7 @@
         <v>402.4</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>2.8</v>
+        <v>32.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>0.1</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>17.6</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>37.4</v>
+        <v>374</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>32.5</v>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>992.7</v>
+        <v>1992.6</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>149.9</v>
@@ -1944,7 +1944,7 @@
         <v>87</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>28.6</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>223.4</v>
+        <v>423.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>32.5</v>
@@ -2120,7 +2120,7 @@
         <v>25.5</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>21.5</v>
+        <v>221.5</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
@@ -2184,7 +2184,7 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
@@ -2211,7 +2211,7 @@
         <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
@@ -2351,7 +2351,7 @@
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>125.5</v>
+        <v>15.5</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>49.2</v>
@@ -2396,10 +2396,10 @@
         <v>126.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>11</v>
+        <v>411</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>8.1</v>
+        <v>27.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>12</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2439,7 +2439,7 @@
         <v>3.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>19</v>
@@ -2469,7 +2469,7 @@
         <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1.7</v>
+        <v>17</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>24.4</v>
@@ -2524,7 +2524,7 @@
         <v>3.6</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>19.5</v>
@@ -2600,7 +2600,7 @@
         <v>12.2</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.9</v>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>20.8</v>
+        <v>40.8</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>29.4</v>
@@ -2858,7 +2858,7 @@
         <v>20.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2.9</v>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1856</v>
+        <v>1856.4</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>150.3</v>
@@ -2940,7 +2940,7 @@
         <v>52.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>91.7</v>
+        <v>91.3</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>10</v>
@@ -3037,7 +3037,7 @@
         <v>0.1</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>18.6</v>
@@ -3629,7 +3629,7 @@
         <v>3.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
@@ -3647,7 +3647,7 @@
         <v>3</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>27.9</v>
+        <v>27.2</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.1</v>
@@ -3659,7 +3659,7 @@
         <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>13.1</v>
+        <v>18.1</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>25.2</v>
@@ -3784,7 +3784,7 @@
         <v>20.2</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>22.1</v>
+        <v>222.1</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>3.9</v>
@@ -3799,7 +3799,7 @@
         <v>0.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>20.4</v>
@@ -3860,13 +3860,13 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>448.8</v>
+        <v>448.2</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>2.9</v>
+        <v>29.4</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1.9</v>
+        <v>19.5</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>24.5</v>
@@ -3911,7 +3911,7 @@
         <v>21.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>58.4</v>
+        <v>57.4</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>16.1</v>
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>64</v>
+        <v>464.2</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>32.8</v>
@@ -4090,7 +4090,7 @@
         <v>23</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>21.4</v>
+        <v>22.4</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.300000000000001</v>
@@ -4145,7 +4145,7 @@
         <v>19.4</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>18.2</v>
+        <v>28.2</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>20.1</v>
@@ -4245,7 +4245,7 @@
         <v>137.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>14</v>
+        <v>414</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>71.5</v>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>5.8</v>
@@ -4277,13 +4277,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>11.7</v>
+        <v>311.7</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>29</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>24</v>
@@ -4301,7 +4301,7 @@
         <v>2.8</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
@@ -4322,7 +4322,7 @@
         <v>26.2</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>21.6</v>
+        <v>221.6</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>22.9</v>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
@@ -751,7 +751,7 @@
         <v>4.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>17.6</v>
@@ -1166,7 +1166,7 @@
         <v>15.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>44.2</v>
+        <v>442.5</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>94.3</v>
@@ -1178,7 +1178,7 @@
         <v>96.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>22.2</v>
+        <v>440.9</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>12.9</v>
@@ -1251,7 +1251,7 @@
         <v>3.1</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>18.2</v>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1992.6</v>
+        <v>19.9</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>149.9</v>
@@ -1844,7 +1844,7 @@
         <v>3.2</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>20.2</v>
@@ -2093,10 +2093,10 @@
         <v>18.2</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>24</v>
@@ -2120,7 +2120,7 @@
         <v>25.5</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>221.5</v>
+        <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
@@ -2184,7 +2184,7 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
@@ -2254,7 +2254,7 @@
         <v>17.2</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>24.5</v>
+        <v>27.5</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>14.6</v>
@@ -2430,7 +2430,7 @@
         <v>12</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2524,7 +2524,7 @@
         <v>3.6</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>19.5</v>
@@ -2569,7 +2569,7 @@
         <v>74.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1856.4</v>
+        <v>185.6</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>150.3</v>
@@ -2940,7 +2940,7 @@
         <v>52.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>91.3</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>10</v>
@@ -2952,7 +2952,7 @@
         <v>25.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>29.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>93.2</v>
@@ -2979,7 +2979,7 @@
         <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>6.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>123.1</v>
@@ -3034,7 +3034,7 @@
         <v>3.2</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>19.2</v>
@@ -3125,7 +3125,7 @@
         <v>20.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>21.5</v>
@@ -3161,7 +3161,7 @@
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>6.9</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>11.8</v>
@@ -3383,7 +3383,7 @@
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>85.40000000000001</v>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>398.9</v>
+        <v>39.8</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>28.6</v>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1683.5</v>
+        <v>168.5</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>150.1</v>
@@ -3562,7 +3562,7 @@
         <v>14.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>139.6</v>
+        <v>189.6</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>115.4</v>
@@ -3623,13 +3623,13 @@
         <v>18.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
@@ -3647,7 +3647,7 @@
         <v>3</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>27.2</v>
+        <v>27.9</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.1</v>
@@ -3784,7 +3784,7 @@
         <v>20.2</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>222.1</v>
+        <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>3.9</v>
@@ -3808,7 +3808,7 @@
         <v>19.1</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>24.2</v>
+        <v>22.2</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>88</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>448.2</v>
+        <v>448.8</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>29.4</v>
+        <v>2.9</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>19.5</v>
@@ -3911,7 +3911,7 @@
         <v>21.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>57.4</v>
+        <v>58.4</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>16.1</v>
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>464.2</v>
+        <v>46.4</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>32.8</v>
@@ -4145,7 +4145,7 @@
         <v>19.4</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>28.2</v>
+        <v>18.2</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>20.1</v>
@@ -4224,7 +4224,7 @@
         <v>116.4</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>109.2</v>
+        <v>109.3</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>121.1</v>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>5.8</v>
@@ -4283,7 +4283,7 @@
         <v>29</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>18.2</v>
+        <v>18.9</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>24</v>
@@ -4301,7 +4301,7 @@
         <v>2.8</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
@@ -4322,7 +4322,7 @@
         <v>26.2</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>221.6</v>
+        <v>21.6</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>22.9</v>
